--- a/data/output/freshmart_reorder_recommendations.xlsx
+++ b/data/output/freshmart_reorder_recommendations.xlsx
@@ -734,10 +734,10 @@
         <v>2538.213863980442</v>
       </c>
       <c r="D2">
-        <v>1605.010616614799</v>
+        <v>1625.595753961918</v>
       </c>
       <c r="E2">
-        <v>3479.534504528342</v>
+        <v>3402.724552937136</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -751,10 +751,10 @@
         <v>2272.4471589985</v>
       </c>
       <c r="D3">
-        <v>1400.105530204589</v>
+        <v>1330.954502843222</v>
       </c>
       <c r="E3">
-        <v>3130.125057557196</v>
+        <v>3136.964107303249</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -768,10 +768,10 @@
         <v>2388.131248876396</v>
       </c>
       <c r="D4">
-        <v>1523.122871741656</v>
+        <v>1452.701452702767</v>
       </c>
       <c r="E4">
-        <v>3298.333979877187</v>
+        <v>3258.374090364691</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -785,10 +785,10 @@
         <v>2374.109008327017</v>
       </c>
       <c r="D5">
-        <v>1495.143933306019</v>
+        <v>1484.170389288133</v>
       </c>
       <c r="E5">
-        <v>3264.838608160838</v>
+        <v>3305.500666115559</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -802,10 +802,10 @@
         <v>2309.745265128678</v>
       </c>
       <c r="D6">
-        <v>1381.571420619871</v>
+        <v>1416.631514335371</v>
       </c>
       <c r="E6">
-        <v>3174.790098415264</v>
+        <v>3249.597160553365</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -819,10 +819,10 @@
         <v>2495.939751370961</v>
       </c>
       <c r="D7">
-        <v>1567.330616507351</v>
+        <v>1567.164263192485</v>
       </c>
       <c r="E7">
-        <v>3454.143779183412</v>
+        <v>3420.976117099639</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -836,10 +836,10 @@
         <v>2350.696435234667</v>
       </c>
       <c r="D8">
-        <v>1456.240413879059</v>
+        <v>1461.956715755828</v>
       </c>
       <c r="E8">
-        <v>3175.767538496524</v>
+        <v>3170.392382128199</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -853,10 +853,10 @@
         <v>2608.614811580176</v>
       </c>
       <c r="D9">
-        <v>1694.258801901822</v>
+        <v>1745.049672344059</v>
       </c>
       <c r="E9">
-        <v>3520.768559193678</v>
+        <v>3533.569840390836</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -870,10 +870,10 @@
         <v>2333.312466990411</v>
       </c>
       <c r="D10">
-        <v>1398.233311033134</v>
+        <v>1368.469661657961</v>
       </c>
       <c r="E10">
-        <v>3334.625343404631</v>
+        <v>3200.46547751929</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -887,10 +887,10 @@
         <v>2447.907740541345</v>
       </c>
       <c r="D11">
-        <v>1557.737906137474</v>
+        <v>1514.203613364905</v>
       </c>
       <c r="E11">
-        <v>3353.582912964948</v>
+        <v>3353.509565941657</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -904,10 +904,10 @@
         <v>2436.374599619479</v>
       </c>
       <c r="D12">
-        <v>1535.832543803074</v>
+        <v>1531.1461384303</v>
       </c>
       <c r="E12">
-        <v>3317.02732709298</v>
+        <v>3334.97456659122</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -921,10 +921,10 @@
         <v>2368.764799017167</v>
       </c>
       <c r="D13">
-        <v>1490.997659323126</v>
+        <v>1493.429261975201</v>
       </c>
       <c r="E13">
-        <v>3294.431238396206</v>
+        <v>3255.494665412687</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -938,10 +938,10 @@
         <v>2548.478571535676</v>
       </c>
       <c r="D14">
-        <v>1658.187316839321</v>
+        <v>1678.740512949086</v>
       </c>
       <c r="E14">
-        <v>3465.50269611893</v>
+        <v>3463.695118374707</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -955,10 +955,10 @@
         <v>2407.428221897731</v>
       </c>
       <c r="D15">
-        <v>1530.166229135062</v>
+        <v>1504.643357061712</v>
       </c>
       <c r="E15">
-        <v>3298.336309150562</v>
+        <v>3287.988581191716</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -972,10 +972,10 @@
         <v>2687.894708654381</v>
       </c>
       <c r="D16">
-        <v>1836.774348622365</v>
+        <v>1750.532605510767</v>
       </c>
       <c r="E16">
-        <v>3650.689885802709</v>
+        <v>3576.354215795448</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -989,10 +989,10 @@
         <v>2438.99926851018</v>
       </c>
       <c r="D17">
-        <v>1557.760120595816</v>
+        <v>1543.498850018023</v>
       </c>
       <c r="E17">
-        <v>3233.692138000153</v>
+        <v>3303.089215921344</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1006,10 +1006,10 @@
         <v>2551.778234935915</v>
       </c>
       <c r="D18">
-        <v>1684.990868316538</v>
+        <v>1665.468759284063</v>
       </c>
       <c r="E18">
-        <v>3448.257753273221</v>
+        <v>3458.116938679588</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1023,10 +1023,10 @@
         <v>2486.556883243582</v>
       </c>
       <c r="D19">
-        <v>1618.213646234077</v>
+        <v>1681.792294977103</v>
       </c>
       <c r="E19">
-        <v>3336.567692453498</v>
+        <v>3394.028991685752</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1040,10 +1040,10 @@
         <v>2324.091961734679</v>
       </c>
       <c r="D20">
-        <v>1441.461029749255</v>
+        <v>1412.46378823053</v>
       </c>
       <c r="E20">
-        <v>3251.628914755138</v>
+        <v>3276.502725102403</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1057,10 +1057,10 @@
         <v>2414.915021361576</v>
       </c>
       <c r="D21">
-        <v>1580.919960392747</v>
+        <v>1570.342090752855</v>
       </c>
       <c r="E21">
-        <v>3361.335434998026</v>
+        <v>3318.341968863238</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1074,10 +1074,10 @@
         <v>2247.582112832796</v>
       </c>
       <c r="D22">
-        <v>1323.619083787284</v>
+        <v>1318.619736430527</v>
       </c>
       <c r="E22">
-        <v>3173.083903298074</v>
+        <v>3068.48769119247</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1091,10 +1091,10 @@
         <v>2593.827584556826</v>
       </c>
       <c r="D23">
-        <v>1703.458350459368</v>
+        <v>1689.551311797798</v>
       </c>
       <c r="E23">
-        <v>3476.525025658128</v>
+        <v>3450.148446808181</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1108,10 +1108,10 @@
         <v>2486.370586029499</v>
       </c>
       <c r="D24">
-        <v>1571.305605505017</v>
+        <v>1563.523630083075</v>
       </c>
       <c r="E24">
-        <v>3356.095519023833</v>
+        <v>3397.090358410834</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1125,10 +1125,10 @@
         <v>2765.27327018613</v>
       </c>
       <c r="D25">
-        <v>1852.726025046932</v>
+        <v>1866.744321872862</v>
       </c>
       <c r="E25">
-        <v>3635.900980860271</v>
+        <v>3638.94529130798</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1142,10 +1142,10 @@
         <v>2835.431864696894</v>
       </c>
       <c r="D26">
-        <v>1909.932632537048</v>
+        <v>1887.828636779074</v>
       </c>
       <c r="E26">
-        <v>3779.114185908555</v>
+        <v>3698.707556774914</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1159,10 +1159,10 @@
         <v>2742.609321678538</v>
       </c>
       <c r="D27">
-        <v>1867.81806038398</v>
+        <v>1834.736168506773</v>
       </c>
       <c r="E27">
-        <v>3552.310494540486</v>
+        <v>3616.323734498645</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1176,10 +1176,10 @@
         <v>2828.413172106698</v>
       </c>
       <c r="D28">
-        <v>1936.92707369768</v>
+        <v>1959.043137808507</v>
       </c>
       <c r="E28">
-        <v>3693.029457296605</v>
+        <v>3805.378854825437</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1193,10 +1193,10 @@
         <v>2589.712622627998</v>
       </c>
       <c r="D29">
-        <v>1688.125642307521</v>
+        <v>1700.364959091044</v>
       </c>
       <c r="E29">
-        <v>3528.452220645758</v>
+        <v>3522.724206350974</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1210,10 +1210,10 @@
         <v>2815.429393284671</v>
       </c>
       <c r="D30">
-        <v>1866.726986674356</v>
+        <v>1914.493677498306</v>
       </c>
       <c r="E30">
-        <v>3699.595234359049</v>
+        <v>3728.514103635403</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1227,10 +1227,10 @@
         <v>2564.848373257245</v>
       </c>
       <c r="D31">
-        <v>1674.25773442114</v>
+        <v>1795.169387415375</v>
       </c>
       <c r="E31">
-        <v>3558.664759620779</v>
+        <v>3504.904993806721</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1244,10 +1244,10 @@
         <v>2716.116838008309</v>
       </c>
       <c r="D32">
-        <v>1885.575465166421</v>
+        <v>1864.32441374282</v>
       </c>
       <c r="E32">
-        <v>3674.176410689148</v>
+        <v>3607.876633891698</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1261,10 +1261,10 @@
         <v>2715.900315105232</v>
       </c>
       <c r="D33">
-        <v>1761.777389622211</v>
+        <v>1852.115663293248</v>
       </c>
       <c r="E33">
-        <v>3677.6117830163</v>
+        <v>3569.945029887449</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1278,10 +1278,10 @@
         <v>2635.319141930727</v>
       </c>
       <c r="D34">
-        <v>1741.755151597861</v>
+        <v>1816.269038376968</v>
       </c>
       <c r="E34">
-        <v>3481.381002379102</v>
+        <v>3533.328673577815</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1295,10 +1295,10 @@
         <v>2806.782747100908</v>
       </c>
       <c r="D35">
-        <v>1895.898385127105</v>
+        <v>1906.045184067045</v>
       </c>
       <c r="E35">
-        <v>3646.155235814808</v>
+        <v>3706.490907071019</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1312,10 +1312,10 @@
         <v>2684.723881573805</v>
       </c>
       <c r="D36">
-        <v>1847.890368835236</v>
+        <v>1846.702475542878</v>
       </c>
       <c r="E36">
-        <v>3552.937436405697</v>
+        <v>3518.24808984842</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1329,10 +1329,10 @@
         <v>3006.39265430342</v>
       </c>
       <c r="D37">
-        <v>2047.074708860591</v>
+        <v>2014.826473378143</v>
       </c>
       <c r="E37">
-        <v>3903.360294586404</v>
+        <v>3891.06400411833</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1346,10 +1346,10 @@
         <v>2800.70668965357</v>
       </c>
       <c r="D38">
-        <v>1939.413547015299</v>
+        <v>1939.506063327107</v>
       </c>
       <c r="E38">
-        <v>3719.849583768043</v>
+        <v>3661.240001659759</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1363,10 +1363,10 @@
         <v>2950.152977506792</v>
       </c>
       <c r="D39">
-        <v>2098.259543359622</v>
+        <v>2041.131835805999</v>
       </c>
       <c r="E39">
-        <v>3837.868012493274</v>
+        <v>3887.077346039778</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1380,10 +1380,10 @@
         <v>2927.998652391061</v>
       </c>
       <c r="D40">
-        <v>2111.105685255824</v>
+        <v>2080.70810618322</v>
       </c>
       <c r="E40">
-        <v>3831.197319263375</v>
+        <v>3895.580291709097</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1397,10 +1397,10 @@
         <v>2828.385026459548</v>
       </c>
       <c r="D41">
-        <v>1891.582724691648</v>
+        <v>1879.966726862561</v>
       </c>
       <c r="E41">
-        <v>3683.617564440598</v>
+        <v>3697.332561110304</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1414,10 +1414,10 @@
         <v>2987.386467704712</v>
       </c>
       <c r="D42">
-        <v>2099.273546435195</v>
+        <v>2057.166708277926</v>
       </c>
       <c r="E42">
-        <v>3945.776212940508</v>
+        <v>3816.720365488771</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1431,10 +1431,10 @@
         <v>2849.863713090254</v>
       </c>
       <c r="D43">
-        <v>1986.77495735098</v>
+        <v>1928.037873470729</v>
       </c>
       <c r="E43">
-        <v>3719.690426361928</v>
+        <v>3721.533125666997</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1448,10 +1448,10 @@
         <v>3148.34615218949</v>
       </c>
       <c r="D44">
-        <v>2257.577600212742</v>
+        <v>2245.246233830156</v>
       </c>
       <c r="E44">
-        <v>4107.044724295466</v>
+        <v>4116.700180846573</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1465,10 +1465,10 @@
         <v>2921.373510485642</v>
       </c>
       <c r="D45">
-        <v>2000.055267803458</v>
+        <v>2018.68602593929</v>
       </c>
       <c r="E45">
-        <v>3839.027255794339</v>
+        <v>3817.52239183643</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1482,10 +1482,10 @@
         <v>3064.866963859199</v>
       </c>
       <c r="D46">
-        <v>2137.615588584749</v>
+        <v>2182.733311873552</v>
       </c>
       <c r="E46">
-        <v>3954.400734456711</v>
+        <v>3898.025203754381</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1499,10 +1499,10 @@
         <v>3049.749681955709</v>
       </c>
       <c r="D47">
-        <v>2176.336109410231</v>
+        <v>2179.178963841467</v>
       </c>
       <c r="E47">
-        <v>3952.783925783314</v>
+        <v>3984.941888076879</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1516,10 +1516,10 @@
         <v>2944.731961457273</v>
       </c>
       <c r="D48">
-        <v>2027.26145335222</v>
+        <v>2083.750576750311</v>
       </c>
       <c r="E48">
-        <v>3812.436912371311</v>
+        <v>3877.724099357172</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1533,10 +1533,10 @@
         <v>3054.218922865599</v>
       </c>
       <c r="D49">
-        <v>2153.74758931993</v>
+        <v>2180.728210572738</v>
       </c>
       <c r="E49">
-        <v>3930.236204047389</v>
+        <v>3987.377014299157</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1550,10 +1550,10 @@
         <v>2814.555884656114</v>
       </c>
       <c r="D50">
-        <v>1877.567160143105</v>
+        <v>1934.629817946899</v>
       </c>
       <c r="E50">
-        <v>3662.492202440942</v>
+        <v>3680.803837859803</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1567,10 +1567,10 @@
         <v>2989.070708470783</v>
       </c>
       <c r="D51">
-        <v>2124.798207885572</v>
+        <v>2028.839679392208</v>
       </c>
       <c r="E51">
-        <v>3905.215332332268</v>
+        <v>3897.505915180836</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1584,10 +1584,10 @@
         <v>2673.042434600186</v>
       </c>
       <c r="D52">
-        <v>1773.971677086521</v>
+        <v>1801.30481475675</v>
       </c>
       <c r="E52">
-        <v>3572.329245656409</v>
+        <v>3618.324904210726</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1601,10 +1601,10 @@
         <v>2809.640184770391</v>
       </c>
       <c r="D53">
-        <v>1929.642948248439</v>
+        <v>2002.513562081381</v>
       </c>
       <c r="E53">
-        <v>3701.906947017456</v>
+        <v>3671.505404019236</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1618,10 +1618,10 @@
         <v>2877.032587605117</v>
       </c>
       <c r="D54">
-        <v>2010.550645988626</v>
+        <v>1923.550799526548</v>
       </c>
       <c r="E54">
-        <v>3721.52861980646</v>
+        <v>3773.974950253084</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1635,10 +1635,10 @@
         <v>2907.41454402842</v>
       </c>
       <c r="D55">
-        <v>2055.765412580782</v>
+        <v>1973.056857089024</v>
       </c>
       <c r="E55">
-        <v>3743.693326386198</v>
+        <v>3845.532997353828</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1652,10 +1652,10 @@
         <v>3148.321482167418</v>
       </c>
       <c r="D56">
-        <v>2199.953765429565</v>
+        <v>2272.551808603366</v>
       </c>
       <c r="E56">
-        <v>4002.032296836417</v>
+        <v>4046.522507783035</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1669,10 +1669,10 @@
         <v>2989.208448806426</v>
       </c>
       <c r="D57">
-        <v>2053.32966211137</v>
+        <v>2106.226873393692</v>
       </c>
       <c r="E57">
-        <v>3883.140655035048</v>
+        <v>3918.197549819457</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1686,10 +1686,10 @@
         <v>3172.286263147368</v>
       </c>
       <c r="D58">
-        <v>2313.391238183953</v>
+        <v>2308.554417057137</v>
       </c>
       <c r="E58">
-        <v>4086.889426247985</v>
+        <v>4064.40851153215</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1703,10 +1703,10 @@
         <v>2794.337050281345</v>
       </c>
       <c r="D59">
-        <v>1927.550792871841</v>
+        <v>1939.254373964051</v>
       </c>
       <c r="E59">
-        <v>3715.279645185502</v>
+        <v>3690.689432282416</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1720,10 +1720,10 @@
         <v>2812.102770083401</v>
       </c>
       <c r="D60">
-        <v>1941.756132740356</v>
+        <v>1928.424569888695</v>
       </c>
       <c r="E60">
-        <v>3653.805310361892</v>
+        <v>3735.890920150875</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1737,10 +1737,10 @@
         <v>2725.530547219743</v>
       </c>
       <c r="D61">
-        <v>1807.505545218813</v>
+        <v>1780.772044654461</v>
       </c>
       <c r="E61">
-        <v>3583.518236219273</v>
+        <v>3602.162874389252</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1754,10 +1754,10 @@
         <v>2599.602946230121</v>
       </c>
       <c r="D62">
-        <v>1618.291732445103</v>
+        <v>1779.990993185537</v>
       </c>
       <c r="E62">
-        <v>3498.740275382928</v>
+        <v>3532.102142894891</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1771,10 +1771,10 @@
         <v>2724.013479105429</v>
       </c>
       <c r="D63">
-        <v>1759.745217425082</v>
+        <v>1778.850847891502</v>
       </c>
       <c r="E63">
-        <v>3631.641549627885</v>
+        <v>3597.022089052189</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1788,10 +1788,10 @@
         <v>2524.945992273323</v>
       </c>
       <c r="D64">
-        <v>1690.568044631931</v>
+        <v>1684.396337295327</v>
       </c>
       <c r="E64">
-        <v>3381.258032915161</v>
+        <v>3440.253686845715</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1805,10 +1805,10 @@
         <v>2754.322450921741</v>
       </c>
       <c r="D65">
-        <v>1824.617015767295</v>
+        <v>1825.886488551812</v>
       </c>
       <c r="E65">
-        <v>3624.292962127231</v>
+        <v>3688.33387712592</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1822,10 +1822,10 @@
         <v>2481.630718123231</v>
       </c>
       <c r="D66">
-        <v>1665.145636318639</v>
+        <v>1584.499678640082</v>
       </c>
       <c r="E66">
-        <v>3395.255956432268</v>
+        <v>3420.083736768287</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1839,10 +1839,10 @@
         <v>2612.755829188844</v>
       </c>
       <c r="D67">
-        <v>1641.684335032714</v>
+        <v>1689.745570506465</v>
       </c>
       <c r="E67">
-        <v>3479.788334960446</v>
+        <v>3499.214102092763</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1856,10 +1856,10 @@
         <v>2603.580926448727</v>
       </c>
       <c r="D68">
-        <v>1734.240294658084</v>
+        <v>1628.173954847102</v>
       </c>
       <c r="E68">
-        <v>3521.150213617837</v>
+        <v>3525.668441674465</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1873,10 +1873,10 @@
         <v>2506.156136135056</v>
       </c>
       <c r="D69">
-        <v>1640.183055398504</v>
+        <v>1640.051473431358</v>
       </c>
       <c r="E69">
-        <v>3404.153609254938</v>
+        <v>3450.449461555746</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1890,10 +1890,10 @@
         <v>2628.586911351027</v>
       </c>
       <c r="D70">
-        <v>1696.127601931264</v>
+        <v>1782.026653779249</v>
       </c>
       <c r="E70">
-        <v>3582.857890110262</v>
+        <v>3517.392197278835</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1907,10 +1907,10 @@
         <v>2424.944991680718</v>
       </c>
       <c r="D71">
-        <v>1522.512118388202</v>
+        <v>1468.861538305316</v>
       </c>
       <c r="E71">
-        <v>3301.959915263673</v>
+        <v>3301.737589735534</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1924,10 +1924,10 @@
         <v>2660.995411240146</v>
       </c>
       <c r="D72">
-        <v>1718.713388842595</v>
+        <v>1774.262278038591</v>
       </c>
       <c r="E72">
-        <v>3514.366937624383</v>
+        <v>3570.472527173648</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1941,10 +1941,10 @@
         <v>2401.159921862885</v>
       </c>
       <c r="D73">
-        <v>1489.753696184059</v>
+        <v>1535.128064169582</v>
       </c>
       <c r="E73">
-        <v>3349.246581779927</v>
+        <v>3330.699354577282</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1958,10 +1958,10 @@
         <v>2541.703229100305</v>
       </c>
       <c r="D74">
-        <v>1628.539510671824</v>
+        <v>1654.478741272439</v>
       </c>
       <c r="E74">
-        <v>3486.384704415724</v>
+        <v>3423.521854752169</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1975,10 +1975,10 @@
         <v>2540.716381455181</v>
       </c>
       <c r="D75">
-        <v>1605.050673287718</v>
+        <v>1619.783719809076</v>
       </c>
       <c r="E75">
-        <v>3433.663249442269</v>
+        <v>3478.074030550064</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1992,10 +1992,10 @@
         <v>2463.750597782293</v>
       </c>
       <c r="D76">
-        <v>1557.010275474599</v>
+        <v>1638.886757627926</v>
       </c>
       <c r="E76">
-        <v>3327.362532570472</v>
+        <v>3306.911094102964</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2009,10 +2009,10 @@
         <v>2626.194679204871</v>
       </c>
       <c r="D77">
-        <v>1706.161384239518</v>
+        <v>1757.933584045983</v>
       </c>
       <c r="E77">
-        <v>3566.302903055222</v>
+        <v>3505.099976580095</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2026,10 +2026,10 @@
         <v>2467.168961794697</v>
       </c>
       <c r="D78">
-        <v>1534.000038657437</v>
+        <v>1544.269480703839</v>
       </c>
       <c r="E78">
-        <v>3334.997084644257</v>
+        <v>3415.402837166859</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2043,10 +2043,10 @@
         <v>2719.911280751579</v>
       </c>
       <c r="D79">
-        <v>1808.114177265258</v>
+        <v>1857.495018379491</v>
       </c>
       <c r="E79">
-        <v>3581.845479996482</v>
+        <v>3565.759772616183</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2060,10 +2060,10 @@
         <v>2424.747877091247</v>
       </c>
       <c r="D80">
-        <v>1511.404605931412</v>
+        <v>1557.907541513341</v>
       </c>
       <c r="E80">
-        <v>3301.520250745049</v>
+        <v>3344.328947507379</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2077,10 +2077,10 @@
         <v>2488.136144257442</v>
       </c>
       <c r="D81">
-        <v>1501.156473724639</v>
+        <v>1557.860261102567</v>
       </c>
       <c r="E81">
-        <v>3405.784860819784</v>
+        <v>3403.321806799725</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2094,10 +2094,10 @@
         <v>2414.856931212105</v>
       </c>
       <c r="D82">
-        <v>1465.882534215482</v>
+        <v>1548.728045212556</v>
       </c>
       <c r="E82">
-        <v>3389.843858281503</v>
+        <v>3333.819251212448</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2111,10 +2111,10 @@
         <v>2326.619887058789</v>
       </c>
       <c r="D83">
-        <v>1426.475206873434</v>
+        <v>1408.348959813268</v>
       </c>
       <c r="E83">
-        <v>3193.574967446961</v>
+        <v>3216.292690979327</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2128,10 +2128,10 @@
         <v>2567.872169240679</v>
       </c>
       <c r="D84">
-        <v>1620.87180344014</v>
+        <v>1658.292874012547</v>
       </c>
       <c r="E84">
-        <v>3462.778159160734</v>
+        <v>3499.213820344096</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2145,10 +2145,10 @@
         <v>2560.963615069109</v>
       </c>
       <c r="D85">
-        <v>1679.960578175194</v>
+        <v>1650.285881889077</v>
       </c>
       <c r="E85">
-        <v>3515.957721441847</v>
+        <v>3364.43495514088</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2162,10 +2162,10 @@
         <v>2987.879927565352</v>
       </c>
       <c r="D86">
-        <v>2077.553203619832</v>
+        <v>2124.862599147463</v>
       </c>
       <c r="E86">
-        <v>3840.612405735656</v>
+        <v>3876.871044516799</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2179,10 +2179,10 @@
         <v>2833.315471525248</v>
       </c>
       <c r="D87">
-        <v>1899.904133222027</v>
+        <v>1900.913324744188</v>
       </c>
       <c r="E87">
-        <v>3714.622140178957</v>
+        <v>3644.129028374079</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2196,10 +2196,10 @@
         <v>2968.538504676342</v>
       </c>
       <c r="D88">
-        <v>2079.161983688331</v>
+        <v>2083.977350322227</v>
       </c>
       <c r="E88">
-        <v>3767.512192363026</v>
+        <v>3882.664247688395</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2213,10 +2213,10 @@
         <v>2889.346999484802</v>
       </c>
       <c r="D89">
-        <v>2057.803051003881</v>
+        <v>1974.08553546503</v>
       </c>
       <c r="E89">
-        <v>3780.348744661362</v>
+        <v>3772.13252038332</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2230,10 +2230,10 @@
         <v>2725.712395655585</v>
       </c>
       <c r="D90">
-        <v>1890.982817922449</v>
+        <v>1759.627703242168</v>
       </c>
       <c r="E90">
-        <v>3663.326707440712</v>
+        <v>3603.634293862715</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2247,10 +2247,10 @@
         <v>2839.339657829114</v>
       </c>
       <c r="D91">
-        <v>1996.385190632944</v>
+        <v>1952.380217471646</v>
       </c>
       <c r="E91">
-        <v>3637.552531350525</v>
+        <v>3721.279241080189</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2264,10 +2264,10 @@
         <v>2790.427302324902</v>
       </c>
       <c r="D92">
-        <v>1877.324061239004</v>
+        <v>1921.609092030971</v>
       </c>
       <c r="E92">
-        <v>3659.182881625701</v>
+        <v>3704.105243068808</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2281,10 +2281,10 @@
         <v>2840.729818563315</v>
       </c>
       <c r="D93">
-        <v>1912.800924618433</v>
+        <v>1939.265191698029</v>
       </c>
       <c r="E93">
-        <v>3777.61434039639</v>
+        <v>3757.755317275728</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2298,10 +2298,10 @@
         <v>2796.30378894349</v>
       </c>
       <c r="D94">
-        <v>1874.886413552367</v>
+        <v>1902.550617781336</v>
       </c>
       <c r="E94">
-        <v>3589.533278618679</v>
+        <v>3614.554006593423</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2315,10 +2315,10 @@
         <v>2843.373843767473</v>
       </c>
       <c r="D95">
-        <v>1935.228114694674</v>
+        <v>1909.517545560113</v>
       </c>
       <c r="E95">
-        <v>3770.453528232867</v>
+        <v>3690.645159277598</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2332,10 +2332,10 @@
         <v>2732.438462064292</v>
       </c>
       <c r="D96">
-        <v>1797.541735904557</v>
+        <v>1834.874101062285</v>
       </c>
       <c r="E96">
-        <v>3680.052787360968</v>
+        <v>3647.177915753289</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2349,10 +2349,10 @@
         <v>2581.210335950675</v>
       </c>
       <c r="D97">
-        <v>1674.496968255557</v>
+        <v>1713.51365777299</v>
       </c>
       <c r="E97">
-        <v>3515.140491558745</v>
+        <v>3551.588090449581</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2366,10 +2366,10 @@
         <v>2447.139331485926</v>
       </c>
       <c r="D98">
-        <v>1600.947634034355</v>
+        <v>1512.882526720831</v>
       </c>
       <c r="E98">
-        <v>3399.500361398395</v>
+        <v>3396.05880872123</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2383,10 +2383,10 @@
         <v>2475.018047131683</v>
       </c>
       <c r="D99">
-        <v>1587.376459916365</v>
+        <v>1636.344446307684</v>
       </c>
       <c r="E99">
-        <v>3394.4364778809</v>
+        <v>3359.432634030441</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2400,10 +2400,10 @@
         <v>2512.423431765695</v>
       </c>
       <c r="D100">
-        <v>1627.201186469094</v>
+        <v>1612.675432214126</v>
       </c>
       <c r="E100">
-        <v>3395.002116636233</v>
+        <v>3393.072499807892</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2417,10 +2417,10 @@
         <v>2511.431111921242</v>
       </c>
       <c r="D101">
-        <v>1591.307810596968</v>
+        <v>1597.70797108778</v>
       </c>
       <c r="E101">
-        <v>3406.479512999204</v>
+        <v>3370.507546218568</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2434,10 +2434,10 @@
         <v>2659.061161097196</v>
       </c>
       <c r="D102">
-        <v>1787.098839633404</v>
+        <v>1795.724082527664</v>
       </c>
       <c r="E102">
-        <v>3493.747437979335</v>
+        <v>3612.756835880588</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2451,10 +2451,10 @@
         <v>2690.396342562523</v>
       </c>
       <c r="D103">
-        <v>1814.109852674487</v>
+        <v>1843.53442055675</v>
       </c>
       <c r="E103">
-        <v>3591.124747862833</v>
+        <v>3613.312642500683</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2468,10 +2468,10 @@
         <v>2692.806377933583</v>
       </c>
       <c r="D104">
-        <v>1804.602453553895</v>
+        <v>1835.043831438984</v>
       </c>
       <c r="E104">
-        <v>3575.58087666017</v>
+        <v>3561.299498090616</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2485,10 +2485,10 @@
         <v>2685.711254189388</v>
       </c>
       <c r="D105">
-        <v>1806.929756954755</v>
+        <v>1740.045280066315</v>
       </c>
       <c r="E105">
-        <v>3557.194037280728</v>
+        <v>3560.690132809409</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2502,10 +2502,10 @@
         <v>2781.410876191163</v>
       </c>
       <c r="D106">
-        <v>1851.488949194831</v>
+        <v>1976.555393108552</v>
       </c>
       <c r="E106">
-        <v>3691.177391931163</v>
+        <v>3694.841303317258</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2519,10 +2519,10 @@
         <v>2813.657747549009</v>
       </c>
       <c r="D107">
-        <v>1938.103261086523</v>
+        <v>1885.318280076628</v>
       </c>
       <c r="E107">
-        <v>3646.321785087592</v>
+        <v>3714.461204242685</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2536,10 +2536,10 @@
         <v>2745.165216936541</v>
       </c>
       <c r="D108">
-        <v>1898.860340723824</v>
+        <v>1783.562773287393</v>
       </c>
       <c r="E108">
-        <v>3606.317702749061</v>
+        <v>3569.801669384625</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2553,10 +2553,10 @@
         <v>2792.651978594534</v>
       </c>
       <c r="D109">
-        <v>1934.03505816582</v>
+        <v>1923.933668408977</v>
       </c>
       <c r="E109">
-        <v>3661.499220557243</v>
+        <v>3686.213279071765</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2570,10 +2570,10 @@
         <v>2726.719902966475</v>
       </c>
       <c r="D110">
-        <v>1825.912283377577</v>
+        <v>1871.372966986443</v>
       </c>
       <c r="E110">
-        <v>3670.694826395345</v>
+        <v>3571.507153192725</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2587,10 +2587,10 @@
         <v>2663.40887130034</v>
       </c>
       <c r="D111">
-        <v>1745.253027618509</v>
+        <v>1819.954582291723</v>
       </c>
       <c r="E111">
-        <v>3578.756713268713</v>
+        <v>3607.609587291336</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2604,10 +2604,10 @@
         <v>2636.966603189656</v>
       </c>
       <c r="D112">
-        <v>1718.196876301967</v>
+        <v>1687.863032821504</v>
       </c>
       <c r="E112">
-        <v>3575.637940668104</v>
+        <v>3568.75904841375</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2621,10 +2621,10 @@
         <v>2760.123808558485</v>
       </c>
       <c r="D113">
-        <v>1879.881895402239</v>
+        <v>1885.834540385361</v>
       </c>
       <c r="E113">
-        <v>3622.931807883662</v>
+        <v>3745.431431456858</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2638,10 +2638,10 @@
         <v>2854.590105973001</v>
       </c>
       <c r="D114">
-        <v>1956.044597596223</v>
+        <v>1989.916864809636</v>
       </c>
       <c r="E114">
-        <v>3728.554535276895</v>
+        <v>3806.86615001337</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2655,10 +2655,10 @@
         <v>2860.808660547546</v>
       </c>
       <c r="D115">
-        <v>2012.660689379491</v>
+        <v>2004.134468672854</v>
       </c>
       <c r="E115">
-        <v>3804.117430578203</v>
+        <v>3739.430573360604</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2672,10 +2672,10 @@
         <v>2966.677910735606</v>
       </c>
       <c r="D116">
-        <v>1978.668164324996</v>
+        <v>2076.898064601631</v>
       </c>
       <c r="E116">
-        <v>3857.798866952088</v>
+        <v>3856.022321700465</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2689,10 +2689,10 @@
         <v>2915.339672515059</v>
       </c>
       <c r="D117">
-        <v>1965.449883729533</v>
+        <v>2010.570526819477</v>
       </c>
       <c r="E117">
-        <v>3890.827879489872</v>
+        <v>3801.111714761993</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2706,10 +2706,10 @@
         <v>2808.923714565216</v>
       </c>
       <c r="D118">
-        <v>1976.369263506471</v>
+        <v>1969.268393456819</v>
       </c>
       <c r="E118">
-        <v>3697.152379955179</v>
+        <v>3700.662354307195</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2723,10 +2723,10 @@
         <v>2690.678255628313</v>
       </c>
       <c r="D119">
-        <v>1723.081372975904</v>
+        <v>1810.140271108159</v>
       </c>
       <c r="E119">
-        <v>3580.620242146892</v>
+        <v>3544.504814834238</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2740,10 +2740,10 @@
         <v>2704.254538144671</v>
       </c>
       <c r="D120">
-        <v>1902.270261891681</v>
+        <v>1800.25015389627</v>
       </c>
       <c r="E120">
-        <v>3598.112616151935</v>
+        <v>3633.640975523481</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2757,10 +2757,10 @@
         <v>2710.032329164569</v>
       </c>
       <c r="D121">
-        <v>1779.640252908755</v>
+        <v>1752.679991991914</v>
       </c>
       <c r="E121">
-        <v>3604.227290977503</v>
+        <v>3553.831304882982</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2774,10 +2774,10 @@
         <v>2674.749030674778</v>
       </c>
       <c r="D122">
-        <v>1751.47469745928</v>
+        <v>1845.563302317811</v>
       </c>
       <c r="E122">
-        <v>3552.759721230071</v>
+        <v>3620.818419407553</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2791,10 +2791,10 @@
         <v>2786.25627987807</v>
       </c>
       <c r="D123">
-        <v>1908.421460508389</v>
+        <v>1906.42086171794</v>
       </c>
       <c r="E123">
-        <v>3675.90842904899</v>
+        <v>3624.551411163271</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2808,10 +2808,10 @@
         <v>2762.407349235412</v>
       </c>
       <c r="D124">
-        <v>1827.55916971691</v>
+        <v>1824.427814909405</v>
       </c>
       <c r="E124">
-        <v>3630.054469936577</v>
+        <v>3668.59675874027</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2825,10 +2825,10 @@
         <v>2670.52499369783</v>
       </c>
       <c r="D125">
-        <v>1759.608158365934</v>
+        <v>1794.938792130632</v>
       </c>
       <c r="E125">
-        <v>3544.408678254897</v>
+        <v>3642.353846981716</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2842,10 +2842,10 @@
         <v>2528.834791404831</v>
       </c>
       <c r="D126">
-        <v>1670.1142799949</v>
+        <v>1634.127935427445</v>
       </c>
       <c r="E126">
-        <v>3400.752673161535</v>
+        <v>3490.971533628157</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2859,10 +2859,10 @@
         <v>2477.561253532084</v>
       </c>
       <c r="D127">
-        <v>1584.959728406619</v>
+        <v>1540.536513168379</v>
       </c>
       <c r="E127">
-        <v>3345.09261561458</v>
+        <v>3386.198462831272</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2876,10 +2876,10 @@
         <v>2394.366373680222</v>
       </c>
       <c r="D128">
-        <v>1467.103216249412</v>
+        <v>1478.990697666306</v>
       </c>
       <c r="E128">
-        <v>3218.319461638509</v>
+        <v>3324.464397785163</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2893,10 +2893,10 @@
         <v>2274.449252541701</v>
       </c>
       <c r="D129">
-        <v>1347.532362684151</v>
+        <v>1342.850020506654</v>
       </c>
       <c r="E129">
-        <v>3131.224237541671</v>
+        <v>3218.912808136803</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2910,10 +2910,10 @@
         <v>2334.231040497178</v>
       </c>
       <c r="D130">
-        <v>1383.443813647328</v>
+        <v>1418.827256334078</v>
       </c>
       <c r="E130">
-        <v>3219.369206607824</v>
+        <v>3161.686941650586</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2927,10 +2927,10 @@
         <v>2312.243927125179</v>
       </c>
       <c r="D131">
-        <v>1419.225902511807</v>
+        <v>1385.901641348118</v>
       </c>
       <c r="E131">
-        <v>3148.052065831102</v>
+        <v>3221.745132234461</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2944,10 +2944,10 @@
         <v>2284.321629067727</v>
       </c>
       <c r="D132">
-        <v>1374.004133434426</v>
+        <v>1387.473850955015</v>
       </c>
       <c r="E132">
-        <v>3186.882451574038</v>
+        <v>3145.857028232061</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2961,10 +2961,10 @@
         <v>2261.912274802923</v>
       </c>
       <c r="D133">
-        <v>1332.488067084531</v>
+        <v>1398.244340902038</v>
       </c>
       <c r="E133">
-        <v>3118.72968967835</v>
+        <v>3128.328361945505</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2978,10 +2978,10 @@
         <v>2362.188798097948</v>
       </c>
       <c r="D134">
-        <v>1439.883951508679</v>
+        <v>1479.53731007554</v>
       </c>
       <c r="E134">
-        <v>3248.88967728459</v>
+        <v>3232.405621219805</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2995,10 +2995,10 @@
         <v>2427.329561740949</v>
       </c>
       <c r="D135">
-        <v>1481.372991493798</v>
+        <v>1564.353397106714</v>
       </c>
       <c r="E135">
-        <v>3303.68295880399</v>
+        <v>3385.379372876638</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3012,10 +3012,10 @@
         <v>2415.4164717364</v>
       </c>
       <c r="D136">
-        <v>1519.260163447549</v>
+        <v>1547.899001620401</v>
       </c>
       <c r="E136">
-        <v>3288.236364563605</v>
+        <v>3364.592044909861</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3029,10 +3029,10 @@
         <v>2518.347196447543</v>
       </c>
       <c r="D137">
-        <v>1625.196047347125</v>
+        <v>1611.970586382827</v>
       </c>
       <c r="E137">
-        <v>3436.008391263742</v>
+        <v>3421.932261829022</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3046,10 +3046,10 @@
         <v>2472.82643076456</v>
       </c>
       <c r="D138">
-        <v>1592.262622094027</v>
+        <v>1555.679489884313</v>
       </c>
       <c r="E138">
-        <v>3337.766050130084</v>
+        <v>3394.830636666779</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3063,10 +3063,10 @@
         <v>2375.919192922049</v>
       </c>
       <c r="D139">
-        <v>1402.704711786491</v>
+        <v>1406.573968299861</v>
       </c>
       <c r="E139">
-        <v>3277.253265121072</v>
+        <v>3269.740549738236</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3080,10 +3080,10 @@
         <v>2273.167547092071</v>
       </c>
       <c r="D140">
-        <v>1415.156708661047</v>
+        <v>1394.332005601768</v>
       </c>
       <c r="E140">
-        <v>3211.177716512773</v>
+        <v>3186.831741274824</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3097,10 +3097,10 @@
         <v>2314.774603300392</v>
       </c>
       <c r="D141">
-        <v>1394.003031484813</v>
+        <v>1355.124909644122</v>
       </c>
       <c r="E141">
-        <v>3225.010841945356</v>
+        <v>3301.516893936726</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3114,10 +3114,10 @@
         <v>2364.478864296963</v>
       </c>
       <c r="D142">
-        <v>1471.336709779302</v>
+        <v>1418.187674681226</v>
       </c>
       <c r="E142">
-        <v>3268.502243818736</v>
+        <v>3268.996277348965</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3131,10 +3131,10 @@
         <v>2387.152706687006</v>
       </c>
       <c r="D143">
-        <v>1507.030495147881</v>
+        <v>1491.240311890749</v>
       </c>
       <c r="E143">
-        <v>3308.748098052118</v>
+        <v>3286.494551034574</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3148,10 +3148,10 @@
         <v>2567.984497738478</v>
       </c>
       <c r="D144">
-        <v>1631.501292157237</v>
+        <v>1658.463739215844</v>
       </c>
       <c r="E144">
-        <v>3432.572969435602</v>
+        <v>3431.147644849192</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3165,10 +3165,10 @@
         <v>2625.449196507887</v>
       </c>
       <c r="D145">
-        <v>1717.533395888378</v>
+        <v>1787.216588988013</v>
       </c>
       <c r="E145">
-        <v>3442.049368792176</v>
+        <v>3566.213058941123</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3182,10 +3182,10 @@
         <v>2629.615319360642</v>
       </c>
       <c r="D146">
-        <v>1751.253852803659</v>
+        <v>1741.230773317549</v>
       </c>
       <c r="E146">
-        <v>3521.218178688144</v>
+        <v>3436.61931727674</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3199,10 +3199,10 @@
         <v>2595.786437704993</v>
       </c>
       <c r="D147">
-        <v>1657.697493333384</v>
+        <v>1682.75376382891</v>
       </c>
       <c r="E147">
-        <v>3457.797271141213</v>
+        <v>3480.462350595444</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3216,10 +3216,10 @@
         <v>2651.253509094636</v>
       </c>
       <c r="D148">
-        <v>1757.586595277171</v>
+        <v>1775.138932941558</v>
       </c>
       <c r="E148">
-        <v>3457.156492280418</v>
+        <v>3571.992534559085</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3233,10 +3233,10 @@
         <v>2655.872478111685</v>
       </c>
       <c r="D149">
-        <v>1719.215235822377</v>
+        <v>1843.161205450848</v>
       </c>
       <c r="E149">
-        <v>3542.273599707771</v>
+        <v>3520.900606250043</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3250,10 +3250,10 @@
         <v>2594.843378896921</v>
       </c>
       <c r="D150">
-        <v>1684.96104394832</v>
+        <v>1650.264357580537</v>
       </c>
       <c r="E150">
-        <v>3485.014669125804</v>
+        <v>3512.165960902291</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3267,10 +3267,10 @@
         <v>2690.117368224305</v>
       </c>
       <c r="D151">
-        <v>1700.088228150552</v>
+        <v>1758.006186110458</v>
       </c>
       <c r="E151">
-        <v>3551.115345419831</v>
+        <v>3603.57699926778</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3284,10 +3284,10 @@
         <v>2694.625310903332</v>
       </c>
       <c r="D152">
-        <v>1768.59429994419</v>
+        <v>1822.251260816676</v>
       </c>
       <c r="E152">
-        <v>3534.87182079982</v>
+        <v>3618.78442285146</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3301,10 +3301,10 @@
         <v>2692.119099158974</v>
       </c>
       <c r="D153">
-        <v>1803.760265372367</v>
+        <v>1762.180608875516</v>
       </c>
       <c r="E153">
-        <v>3600.700270845423</v>
+        <v>3540.279472795785</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3318,10 +3318,10 @@
         <v>2683.766110591286</v>
       </c>
       <c r="D154">
-        <v>1788.329397340922</v>
+        <v>1754.399132590426</v>
       </c>
       <c r="E154">
-        <v>3572.267091879937</v>
+        <v>3572.388438275287</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3335,10 +3335,10 @@
         <v>2764.200369027207</v>
       </c>
       <c r="D155">
-        <v>1862.795885700094</v>
+        <v>1867.546002098836</v>
       </c>
       <c r="E155">
-        <v>3647.829201839928</v>
+        <v>3577.119406239935</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3352,10 +3352,10 @@
         <v>2761.067907204494</v>
       </c>
       <c r="D156">
-        <v>1815.817849229189</v>
+        <v>1868.050095491656</v>
       </c>
       <c r="E156">
-        <v>3712.213827479976</v>
+        <v>3714.31905047858</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3369,10 +3369,10 @@
         <v>2644.699922256203</v>
       </c>
       <c r="D157">
-        <v>1708.063688846098</v>
+        <v>1795.216884668392</v>
       </c>
       <c r="E157">
-        <v>3541.197012592322</v>
+        <v>3649.442648181799</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3386,10 +3386,10 @@
         <v>2645.076155733633</v>
       </c>
       <c r="D158">
-        <v>1730.822937393892</v>
+        <v>1764.286460919442</v>
       </c>
       <c r="E158">
-        <v>3578.952439979019</v>
+        <v>3562.892036990088</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3403,10 +3403,10 @@
         <v>2539.771928491552</v>
       </c>
       <c r="D159">
-        <v>1633.909532451808</v>
+        <v>1668.958183912472</v>
       </c>
       <c r="E159">
-        <v>3416.130124605709</v>
+        <v>3477.168932387928</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3420,10 +3420,10 @@
         <v>2442.752944579405</v>
       </c>
       <c r="D160">
-        <v>1556.593899780756</v>
+        <v>1623.262856640756</v>
       </c>
       <c r="E160">
-        <v>3342.398050329539</v>
+        <v>3386.96232347221</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3437,10 +3437,10 @@
         <v>2381.099945429971</v>
       </c>
       <c r="D161">
-        <v>1526.410059256595</v>
+        <v>1463.127519760882</v>
       </c>
       <c r="E161">
-        <v>3238.56240672162</v>
+        <v>3279.676424972862</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3454,10 +3454,10 @@
         <v>2465.156360123746</v>
       </c>
       <c r="D162">
-        <v>1532.751717625335</v>
+        <v>1624.839409862871</v>
       </c>
       <c r="E162">
-        <v>3360.890429713705</v>
+        <v>3347.753718776779</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3471,10 +3471,10 @@
         <v>2524.340555715501</v>
       </c>
       <c r="D163">
-        <v>1680.369414144366</v>
+        <v>1614.566099990777</v>
       </c>
       <c r="E163">
-        <v>3327.952920482122</v>
+        <v>3398.877670498652</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3488,10 +3488,10 @@
         <v>2514.625251829616</v>
       </c>
       <c r="D164">
-        <v>1615.995058139837</v>
+        <v>1650.963991197243</v>
       </c>
       <c r="E164">
-        <v>3326.901758719147</v>
+        <v>3397.70613657661</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3505,10 +3505,10 @@
         <v>2636.563147150083</v>
       </c>
       <c r="D165">
-        <v>1791.628301165745</v>
+        <v>1797.170490916723</v>
       </c>
       <c r="E165">
-        <v>3561.724356368139</v>
+        <v>3522.607004727639</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3522,10 +3522,10 @@
         <v>2630.386189195921</v>
       </c>
       <c r="D166">
-        <v>1682.21096486049</v>
+        <v>1747.17617394489</v>
       </c>
       <c r="E166">
-        <v>3551.357561296434</v>
+        <v>3512.951680439242</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3539,10 +3539,10 @@
         <v>2578.218054817908</v>
       </c>
       <c r="D167">
-        <v>1710.486127572058</v>
+        <v>1724.211240759142</v>
       </c>
       <c r="E167">
-        <v>3363.092531471249</v>
+        <v>3522.800963224318</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3556,10 +3556,10 @@
         <v>2493.93277292835</v>
       </c>
       <c r="D168">
-        <v>1572.122168231503</v>
+        <v>1588.728773167585</v>
       </c>
       <c r="E168">
-        <v>3418.149257752372</v>
+        <v>3346.557128585218</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3573,10 +3573,10 @@
         <v>2499.02844215084</v>
       </c>
       <c r="D169">
-        <v>1620.491337002056</v>
+        <v>1640.723220173579</v>
       </c>
       <c r="E169">
-        <v>3351.559121922088</v>
+        <v>3411.541668244715</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3590,10 +3590,10 @@
         <v>2452.871835446927</v>
       </c>
       <c r="D170">
-        <v>1543.309070295169</v>
+        <v>1613.304799048575</v>
       </c>
       <c r="E170">
-        <v>3355.954007843406</v>
+        <v>3346.386498506645</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3607,10 +3607,10 @@
         <v>2347.211726137322</v>
       </c>
       <c r="D171">
-        <v>1464.530158474414</v>
+        <v>1518.850601919426</v>
       </c>
       <c r="E171">
-        <v>3252.098549515861</v>
+        <v>3236.316779917862</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3624,10 +3624,10 @@
         <v>2411.304124119217</v>
       </c>
       <c r="D172">
-        <v>1529.634325787854</v>
+        <v>1495.698021234437</v>
       </c>
       <c r="E172">
-        <v>3304.261746265207</v>
+        <v>3358.642210420955</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3641,10 +3641,10 @@
         <v>2399.922728955397</v>
       </c>
       <c r="D173">
-        <v>1502.889113652445</v>
+        <v>1530.18552380373</v>
       </c>
       <c r="E173">
-        <v>3265.390236424331</v>
+        <v>3329.558125263966</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3658,10 +3658,10 @@
         <v>2395.206384533253</v>
       </c>
       <c r="D174">
-        <v>1493.632447851194</v>
+        <v>1507.601048707595</v>
       </c>
       <c r="E174">
-        <v>3351.686881181836</v>
+        <v>3333.138604348444</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3675,10 +3675,10 @@
         <v>2398.447298556806</v>
       </c>
       <c r="D175">
-        <v>1524.40791751102</v>
+        <v>1448.262468972952</v>
       </c>
       <c r="E175">
-        <v>3281.895679243786</v>
+        <v>3336.650682328913</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3692,10 +3692,10 @@
         <v>2508.166155879693</v>
       </c>
       <c r="D176">
-        <v>1632.414397083747</v>
+        <v>1584.85521437916</v>
       </c>
       <c r="E176">
-        <v>3392.480660173839</v>
+        <v>3342.476414744642</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3709,10 +3709,10 @@
         <v>2553.921345805214</v>
       </c>
       <c r="D177">
-        <v>1671.568593743018</v>
+        <v>1622.46897053268</v>
       </c>
       <c r="E177">
-        <v>3546.901659469793</v>
+        <v>3447.867136450096</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3726,10 +3726,10 @@
         <v>2499.089312369839</v>
       </c>
       <c r="D178">
-        <v>1584.356915198723</v>
+        <v>1574.814624651038</v>
       </c>
       <c r="E178">
-        <v>3394.827051932566</v>
+        <v>3334.128529426403</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3743,10 +3743,10 @@
         <v>2558.037927555006</v>
       </c>
       <c r="D179">
-        <v>1694.932141666852</v>
+        <v>1592.289770309654</v>
       </c>
       <c r="E179">
-        <v>3411.678656219789</v>
+        <v>3432.806468402721</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3760,10 +3760,10 @@
         <v>2493.467290372888</v>
       </c>
       <c r="D180">
-        <v>1605.506457949819</v>
+        <v>1544.481814911362</v>
       </c>
       <c r="E180">
-        <v>3468.959509017136</v>
+        <v>3408.651296867753</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3777,10 +3777,10 @@
         <v>2417.47540246771</v>
       </c>
       <c r="D181">
-        <v>1565.526173685086</v>
+        <v>1528.451319858215</v>
       </c>
       <c r="E181">
-        <v>3310.690733790833</v>
+        <v>3313.418506200807</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3794,10 +3794,10 @@
         <v>2543.776133937055</v>
       </c>
       <c r="D182">
-        <v>1565.483333856225</v>
+        <v>1585.933780768197</v>
       </c>
       <c r="E182">
-        <v>3444.315206261206</v>
+        <v>3535.12888448655</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3811,10 +3811,10 @@
         <v>2450.158013831704</v>
       </c>
       <c r="D183">
-        <v>1488.943144988942</v>
+        <v>1482.047860927659</v>
       </c>
       <c r="E183">
-        <v>3373.168958712827</v>
+        <v>3401.061737115424</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3828,10 +3828,10 @@
         <v>2615.456485477166</v>
       </c>
       <c r="D184">
-        <v>1740.494694318611</v>
+        <v>1707.329383390181</v>
       </c>
       <c r="E184">
-        <v>3532.205751696796</v>
+        <v>3546.0112896859</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3845,10 +3845,10 @@
         <v>2531.479008058216</v>
       </c>
       <c r="D185">
-        <v>1660.943653837024</v>
+        <v>1537.08142162489</v>
       </c>
       <c r="E185">
-        <v>3446.352073217876</v>
+        <v>3493.222295044758</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3862,10 +3862,10 @@
         <v>2667.366335411332</v>
       </c>
       <c r="D186">
-        <v>1728.282204259024</v>
+        <v>1623.824177036502</v>
       </c>
       <c r="E186">
-        <v>3557.940690671213</v>
+        <v>3600.929201754644</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3879,10 +3879,10 @@
         <v>2768.611815833373</v>
       </c>
       <c r="D187">
-        <v>1756.777970135981</v>
+        <v>1850.964367538602</v>
       </c>
       <c r="E187">
-        <v>3702.29844097351</v>
+        <v>3694.304582804449</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3896,10 +3896,10 @@
         <v>2808.110680171459</v>
       </c>
       <c r="D188">
-        <v>1794.566825788632</v>
+        <v>1879.356412311519</v>
       </c>
       <c r="E188">
-        <v>3732.706407508792</v>
+        <v>3734.482699311097</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3913,10 +3913,10 @@
         <v>2779.125678278426</v>
       </c>
       <c r="D189">
-        <v>1812.44872807654</v>
+        <v>1805.185157278122</v>
       </c>
       <c r="E189">
-        <v>3775.91152109377</v>
+        <v>3729.821308374984</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3930,10 +3930,10 @@
         <v>2728.684602412874</v>
       </c>
       <c r="D190">
-        <v>1726.829530323498</v>
+        <v>1755.560708696194</v>
       </c>
       <c r="E190">
-        <v>3700.62724617773</v>
+        <v>3687.940644063008</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3947,10 +3947,10 @@
         <v>2877.313770028231</v>
       </c>
       <c r="D191">
-        <v>1944.670772827233</v>
+        <v>1879.155830877922</v>
       </c>
       <c r="E191">
-        <v>3838.563555440129</v>
+        <v>3788.147581676329</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3964,10 +3964,10 @@
         <v>2745.111468785208</v>
       </c>
       <c r="D192">
-        <v>1750.503250428812</v>
+        <v>1791.789063976508</v>
       </c>
       <c r="E192">
-        <v>3668.492018398084</v>
+        <v>3702.227896206875</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3981,10 +3981,10 @@
         <v>2838.191326629829</v>
       </c>
       <c r="D193">
-        <v>1851.002184097698</v>
+        <v>1960.064513447045</v>
       </c>
       <c r="E193">
-        <v>3845.6202299659</v>
+        <v>3766.417044685805</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3998,10 +3998,10 @@
         <v>2923.426380486113</v>
       </c>
       <c r="D194">
-        <v>1988.088786981327</v>
+        <v>1954.508616061667</v>
       </c>
       <c r="E194">
-        <v>3859.056984606445</v>
+        <v>3872.262710168199</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4015,10 +4015,10 @@
         <v>2972.286160702646</v>
       </c>
       <c r="D195">
-        <v>2094.969767193334</v>
+        <v>1986.467536879468</v>
       </c>
       <c r="E195">
-        <v>3959.596446102778</v>
+        <v>3902.620989562829</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4032,10 +4032,10 @@
         <v>2964.154233648576</v>
       </c>
       <c r="D196">
-        <v>2045.735580908244</v>
+        <v>2006.453387330769</v>
       </c>
       <c r="E196">
-        <v>3871.600384357643</v>
+        <v>3879.802825097227</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4049,10 +4049,10 @@
         <v>2935.601376676172</v>
       </c>
       <c r="D197">
-        <v>1958.568087521394</v>
+        <v>1979.776920840438</v>
       </c>
       <c r="E197">
-        <v>3811.059835429981</v>
+        <v>3908.3075449458</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4066,10 +4066,10 @@
         <v>3106.508883208147</v>
       </c>
       <c r="D198">
-        <v>2204.457752557528</v>
+        <v>2157.321767410156</v>
       </c>
       <c r="E198">
-        <v>4035.148488323447</v>
+        <v>4053.953945485812</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4083,10 +4083,10 @@
         <v>2998.678491017233</v>
       </c>
       <c r="D199">
-        <v>1984.494660683159</v>
+        <v>2110.467555298876</v>
       </c>
       <c r="E199">
-        <v>3940.735464691151</v>
+        <v>4002.576103552804</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4100,10 +4100,10 @@
         <v>3111.949100866194</v>
       </c>
       <c r="D200">
-        <v>2134.708417325404</v>
+        <v>2156.482699192397</v>
       </c>
       <c r="E200">
-        <v>4022.611350380775</v>
+        <v>4060.619805117349</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4117,10 +4117,10 @@
         <v>3195.854627046474</v>
       </c>
       <c r="D201">
-        <v>2320.843490010119</v>
+        <v>2260.061584431824</v>
       </c>
       <c r="E201">
-        <v>4120.610458607779</v>
+        <v>4081.425744194591</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4134,10 +4134,10 @@
         <v>3204.106565547848</v>
       </c>
       <c r="D202">
-        <v>2317.468417113752</v>
+        <v>2246.701522223565</v>
       </c>
       <c r="E202">
-        <v>4135.462738490255</v>
+        <v>4144.576689880042</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4151,10 +4151,10 @@
         <v>3112.272875077458</v>
       </c>
       <c r="D203">
-        <v>2147.989031182588</v>
+        <v>2120.762470105426</v>
       </c>
       <c r="E203">
-        <v>4061.693084233504</v>
+        <v>4074.45946199689</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4168,10 +4168,10 @@
         <v>2973.393721368184</v>
       </c>
       <c r="D204">
-        <v>2038.459078829132</v>
+        <v>2061.517749966483</v>
       </c>
       <c r="E204">
-        <v>3880.28572713704</v>
+        <v>3906.227197821118</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4185,10 +4185,10 @@
         <v>3037.137920985757</v>
       </c>
       <c r="D205">
-        <v>2125.795398075878</v>
+        <v>2134.337544803221</v>
       </c>
       <c r="E205">
-        <v>3997.027571570809</v>
+        <v>3981.428548345412</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4202,10 +4202,10 @@
         <v>2853.368614740208</v>
       </c>
       <c r="D206">
-        <v>1918.72563749682</v>
+        <v>1986.34910931718</v>
       </c>
       <c r="E206">
-        <v>3846.816849204241</v>
+        <v>3829.700422443506</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4219,10 +4219,10 @@
         <v>2937.154222623899</v>
       </c>
       <c r="D207">
-        <v>1985.600528278532</v>
+        <v>1989.92897593605</v>
       </c>
       <c r="E207">
-        <v>3856.08619095139</v>
+        <v>3850.374025839176</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4236,10 +4236,10 @@
         <v>3036.513927517177</v>
       </c>
       <c r="D208">
-        <v>2126.112000262113</v>
+        <v>2036.566377165395</v>
       </c>
       <c r="E208">
-        <v>4009.703086253682</v>
+        <v>4023.887083869147</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4253,10 +4253,10 @@
         <v>3090.850645783453</v>
       </c>
       <c r="D209">
-        <v>2150.584034999504</v>
+        <v>2178.30609975653</v>
       </c>
       <c r="E209">
-        <v>4074.611159460166</v>
+        <v>4035.609989391449</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4270,10 +4270,10 @@
         <v>3053.562078400009</v>
       </c>
       <c r="D210">
-        <v>2128.402981693715</v>
+        <v>2153.660351809855</v>
       </c>
       <c r="E210">
-        <v>3932.94968961595</v>
+        <v>3991.613533719856</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4287,10 +4287,10 @@
         <v>2952.409594618246</v>
       </c>
       <c r="D211">
-        <v>1999.277132044759</v>
+        <v>2013.865449620858</v>
       </c>
       <c r="E211">
-        <v>3873.558321344986</v>
+        <v>3910.761009084451</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4304,10 +4304,10 @@
         <v>3015.707297843564</v>
       </c>
       <c r="D212">
-        <v>2075.62872599886</v>
+        <v>2116.792030535492</v>
       </c>
       <c r="E212">
-        <v>3980.159000286663</v>
+        <v>3943.21564015255</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4321,10 +4321,10 @@
         <v>2785.968753197462</v>
       </c>
       <c r="D213">
-        <v>1901.853991666138</v>
+        <v>1806.66887252458</v>
       </c>
       <c r="E213">
-        <v>3743.285380490231</v>
+        <v>3715.758398167335</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4338,10 +4338,10 @@
         <v>2794.424371141408</v>
       </c>
       <c r="D214">
-        <v>1891.968663026362</v>
+        <v>1816.190052626528</v>
       </c>
       <c r="E214">
-        <v>3843.851348210848</v>
+        <v>3805.558730208105</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4355,10 +4355,10 @@
         <v>2825.804601733821</v>
       </c>
       <c r="D215">
-        <v>1858.147976778118</v>
+        <v>1897.499841991229</v>
       </c>
       <c r="E215">
-        <v>3726.498404796274</v>
+        <v>3761.877287149796</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4372,10 +4372,10 @@
         <v>2859.860976837008</v>
       </c>
       <c r="D216">
-        <v>1874.805633455297</v>
+        <v>1959.386962784091</v>
       </c>
       <c r="E216">
-        <v>3724.076852209473</v>
+        <v>3783.544512076263</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4389,10 +4389,10 @@
         <v>2869.425754917425</v>
       </c>
       <c r="D217">
-        <v>1886.355790033165</v>
+        <v>1868.584284890987</v>
       </c>
       <c r="E217">
-        <v>3802.89404379186</v>
+        <v>3836.766725711543</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4406,10 +4406,10 @@
         <v>2865.958228417939</v>
       </c>
       <c r="D218">
-        <v>1828.281496968661</v>
+        <v>1935.755891350489</v>
       </c>
       <c r="E218">
-        <v>3770.255532918285</v>
+        <v>3777.44071579606</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4423,10 +4423,10 @@
         <v>3033.216291456152</v>
       </c>
       <c r="D219">
-        <v>2062.844108361833</v>
+        <v>2071.202408738779</v>
       </c>
       <c r="E219">
-        <v>4020.303353588215</v>
+        <v>3993.236430528114</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4440,10 +4440,10 @@
         <v>2867.155327488054</v>
       </c>
       <c r="D220">
-        <v>1874.357163173934</v>
+        <v>1982.068867811213</v>
       </c>
       <c r="E220">
-        <v>3821.071108834961</v>
+        <v>3823.367770286119</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4457,10 +4457,10 @@
         <v>2878.940967792738</v>
       </c>
       <c r="D221">
-        <v>1899.007862554965</v>
+        <v>1885.698607981856</v>
       </c>
       <c r="E221">
-        <v>3861.039831214318</v>
+        <v>3786.202576655987</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4474,10 +4474,10 @@
         <v>2868.317232369925</v>
       </c>
       <c r="D222">
-        <v>1971.716764470793</v>
+        <v>1953.689165481559</v>
       </c>
       <c r="E222">
-        <v>3770.646980692031</v>
+        <v>3824.594697721042</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4491,10 +4491,10 @@
         <v>2851.054168228013</v>
       </c>
       <c r="D223">
-        <v>1910.609764532609</v>
+        <v>1911.029127476581</v>
       </c>
       <c r="E223">
-        <v>3841.19195886618</v>
+        <v>3816.245863039494</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4508,10 +4508,10 @@
         <v>2831.268399772116</v>
       </c>
       <c r="D224">
-        <v>1908.092070979152</v>
+        <v>1866.960765909147</v>
       </c>
       <c r="E224">
-        <v>3762.90680520555</v>
+        <v>3815.386858249632</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4525,10 +4525,10 @@
         <v>2829.996143039953</v>
       </c>
       <c r="D225">
-        <v>1929.669235134147</v>
+        <v>1898.039714595103</v>
       </c>
       <c r="E225">
-        <v>3799.566116041673</v>
+        <v>3774.801423659456</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4542,10 +4542,10 @@
         <v>3021.178702663059</v>
       </c>
       <c r="D226">
-        <v>2021.252537092236</v>
+        <v>2047.987568918994</v>
       </c>
       <c r="E226">
-        <v>3917.862930194775</v>
+        <v>3931.30645955854</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4559,10 +4559,10 @@
         <v>2886.470164882371</v>
       </c>
       <c r="D227">
-        <v>1895.443372300673</v>
+        <v>1951.593949133331</v>
       </c>
       <c r="E227">
-        <v>3818.331041899576</v>
+        <v>3816.385458929023</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4576,10 +4576,10 @@
         <v>2931.529385177825</v>
       </c>
       <c r="D228">
-        <v>1965.532995274448</v>
+        <v>1901.138664825084</v>
       </c>
       <c r="E228">
-        <v>3914.90472992949</v>
+        <v>3837.540938985954</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4593,10 +4593,10 @@
         <v>2957.796590225294</v>
       </c>
       <c r="D229">
-        <v>2011.358136962936</v>
+        <v>2036.782997822075</v>
       </c>
       <c r="E229">
-        <v>3899.511507261167</v>
+        <v>3811.963817932087</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4610,10 +4610,10 @@
         <v>2979.549215805168</v>
       </c>
       <c r="D230">
-        <v>1984.424673473109</v>
+        <v>2037.501388058708</v>
       </c>
       <c r="E230">
-        <v>3956.358595973334</v>
+        <v>3911.972073959344</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4627,10 +4627,10 @@
         <v>2988.158268902112</v>
       </c>
       <c r="D231">
-        <v>2024.464818877486</v>
+        <v>1945.104340251468</v>
       </c>
       <c r="E231">
-        <v>3959.23231409667</v>
+        <v>3903.922708778563</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4644,10 +4644,10 @@
         <v>2985.000661345762</v>
       </c>
       <c r="D232">
-        <v>2129.132347431414</v>
+        <v>2030.001045293818</v>
       </c>
       <c r="E232">
-        <v>3960.287366180901</v>
+        <v>3917.05444803846</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4661,10 +4661,10 @@
         <v>3131.451344426593</v>
       </c>
       <c r="D233">
-        <v>2182.770182386658</v>
+        <v>2160.182303854371</v>
       </c>
       <c r="E233">
-        <v>4084.271854035073</v>
+        <v>4155.849549501394</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4678,10 +4678,10 @@
         <v>2915.042455426054</v>
       </c>
       <c r="D234">
-        <v>1997.385327742242</v>
+        <v>1931.314463844423</v>
       </c>
       <c r="E234">
-        <v>3885.051794859343</v>
+        <v>3817.941781932814</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4695,10 +4695,10 @@
         <v>2866.091083817331</v>
       </c>
       <c r="D235">
-        <v>1928.6044204477</v>
+        <v>1982.825918366285</v>
       </c>
       <c r="E235">
-        <v>3844.466112446378</v>
+        <v>3822.159867888903</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4712,10 +4712,10 @@
         <v>2816.61408787219</v>
       </c>
       <c r="D236">
-        <v>1873.89725008011</v>
+        <v>1899.304358845438</v>
       </c>
       <c r="E236">
-        <v>3766.052572346436</v>
+        <v>3794.33447693055</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4729,10 +4729,10 @@
         <v>2803.309612241349</v>
       </c>
       <c r="D237">
-        <v>1913.054903873431</v>
+        <v>1816.810490103684</v>
       </c>
       <c r="E237">
-        <v>3748.781665026996</v>
+        <v>3778.986479311043</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4746,10 +4746,10 @@
         <v>2823.98740692615</v>
       </c>
       <c r="D238">
-        <v>1859.234084610373</v>
+        <v>1798.657443947971</v>
       </c>
       <c r="E238">
-        <v>3776.303710399507</v>
+        <v>3772.328349158689</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4763,10 +4763,10 @@
         <v>2871.316673400751</v>
       </c>
       <c r="D239">
-        <v>1957.133163719346</v>
+        <v>1912.254685553011</v>
       </c>
       <c r="E239">
-        <v>3832.63654402277</v>
+        <v>3809.904294751725</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4780,10 +4780,10 @@
         <v>3087.714475321241</v>
       </c>
       <c r="D240">
-        <v>2165.285201450559</v>
+        <v>2086.854444054432</v>
       </c>
       <c r="E240">
-        <v>3970.771967531934</v>
+        <v>3986.801355164272</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4797,10 +4797,10 @@
         <v>2935.894463373608</v>
       </c>
       <c r="D241">
-        <v>2061.98315868286</v>
+        <v>2002.849734599908</v>
       </c>
       <c r="E241">
-        <v>3920.986397114084</v>
+        <v>3832.726029801525</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4814,10 +4814,10 @@
         <v>2921.708476172578</v>
       </c>
       <c r="D242">
-        <v>2007.121412436356</v>
+        <v>2004.605245328363</v>
       </c>
       <c r="E242">
-        <v>3886.963527927957</v>
+        <v>3830.941873240052</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4831,10 +4831,10 @@
         <v>2861.23225840346</v>
       </c>
       <c r="D243">
-        <v>1971.212905421715</v>
+        <v>1951.446756607917</v>
       </c>
       <c r="E243">
-        <v>3789.890460784454</v>
+        <v>3824.082401716164</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4848,10 +4848,10 @@
         <v>2794.856974915066</v>
       </c>
       <c r="D244">
-        <v>1842.527314521392</v>
+        <v>1862.168721037205</v>
       </c>
       <c r="E244">
-        <v>3686.99780296836</v>
+        <v>3643.50630161199</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4865,10 +4865,10 @@
         <v>2747.990001464329</v>
       </c>
       <c r="D245">
-        <v>1885.694378749471</v>
+        <v>1806.587041453997</v>
       </c>
       <c r="E245">
-        <v>3649.297824362162</v>
+        <v>3736.457988930194</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4882,10 +4882,10 @@
         <v>2754.859019776914</v>
       </c>
       <c r="D246">
-        <v>1801.014204077004</v>
+        <v>1890.063149776183</v>
       </c>
       <c r="E246">
-        <v>3727.070400747276</v>
+        <v>3787.628982111079</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4899,10 +4899,10 @@
         <v>2990.74637089344</v>
       </c>
       <c r="D247">
-        <v>2025.639999479347</v>
+        <v>2070.507082569301</v>
       </c>
       <c r="E247">
-        <v>3908.385747493121</v>
+        <v>3907.507824161838</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4916,10 +4916,10 @@
         <v>2920.275912347116</v>
       </c>
       <c r="D248">
-        <v>1950.290966969202</v>
+        <v>1953.076672998927</v>
       </c>
       <c r="E248">
-        <v>3858.427483190298</v>
+        <v>3847.589419467204</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4933,10 +4933,10 @@
         <v>3016.528137106355</v>
       </c>
       <c r="D249">
-        <v>2134.633707457058</v>
+        <v>2112.081912786008</v>
       </c>
       <c r="E249">
-        <v>4006.994332506871</v>
+        <v>3957.6823891824</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4950,10 +4950,10 @@
         <v>3045.952993474919</v>
       </c>
       <c r="D250">
-        <v>2069.016703607244</v>
+        <v>2172.474191507715</v>
       </c>
       <c r="E250">
-        <v>3987.726512553345</v>
+        <v>4031.961997296544</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4967,10 +4967,10 @@
         <v>3012.887727650544</v>
       </c>
       <c r="D251">
-        <v>2114.581553385415</v>
+        <v>2107.972678108851</v>
       </c>
       <c r="E251">
-        <v>3912.319903635316</v>
+        <v>4004.345766427266</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4984,10 +4984,10 @@
         <v>2940.58452494219</v>
       </c>
       <c r="D252">
-        <v>1955.982030454205</v>
+        <v>1950.29136045146</v>
       </c>
       <c r="E252">
-        <v>3926.932702434246</v>
+        <v>3884.501955644324</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5001,10 +5001,10 @@
         <v>2891.897380700406</v>
       </c>
       <c r="D253">
-        <v>1981.568834310464</v>
+        <v>1927.554249019512</v>
       </c>
       <c r="E253">
-        <v>3869.107095572741</v>
+        <v>3802.229954214889</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5018,10 +5018,10 @@
         <v>3079.038303195022</v>
       </c>
       <c r="D254">
-        <v>2117.979647750511</v>
+        <v>2183.181200601955</v>
       </c>
       <c r="E254">
-        <v>4000.304030124684</v>
+        <v>4024.065465816491</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5035,10 +5035,10 @@
         <v>2987.88006097615</v>
       </c>
       <c r="D255">
-        <v>2011.15413290952</v>
+        <v>2031.049316232342</v>
       </c>
       <c r="E255">
-        <v>3931.035705170362</v>
+        <v>3934.530671792227</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5052,10 +5052,10 @@
         <v>3090.17203208718</v>
       </c>
       <c r="D256">
-        <v>2206.359660362801</v>
+        <v>2130.55104865632</v>
       </c>
       <c r="E256">
-        <v>4054.726541973273</v>
+        <v>4084.434084018955</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5069,10 +5069,10 @@
         <v>3138.187781883377</v>
       </c>
       <c r="D257">
-        <v>2224.534739695207</v>
+        <v>2196.615293761645</v>
       </c>
       <c r="E257">
-        <v>4080.543029633527</v>
+        <v>4072.178925434278</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5086,10 +5086,10 @@
         <v>3125.587891661277</v>
       </c>
       <c r="D258">
-        <v>2210.618668033198</v>
+        <v>2207.790105485454</v>
       </c>
       <c r="E258">
-        <v>4050.20014223302</v>
+        <v>4071.122769488244</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5103,10 +5103,10 @@
         <v>3074.719766806108</v>
       </c>
       <c r="D259">
-        <v>2162.796662553111</v>
+        <v>2211.071644989848</v>
       </c>
       <c r="E259">
-        <v>4003.68124347862</v>
+        <v>4042.174344606462</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5120,10 +5120,10 @@
         <v>3050.216484259653</v>
       </c>
       <c r="D260">
-        <v>2128.088296769415</v>
+        <v>2142.252289359367</v>
       </c>
       <c r="E260">
-        <v>4014.145404649798</v>
+        <v>4020.762766964572</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5137,10 +5137,10 @@
         <v>3257.693787121611</v>
       </c>
       <c r="D261">
-        <v>2215.865275152735</v>
+        <v>2334.344797362256</v>
       </c>
       <c r="E261">
-        <v>4186.837631484788</v>
+        <v>4213.330269368032</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5154,10 +5154,10 @@
         <v>3165.341447981673</v>
       </c>
       <c r="D262">
-        <v>2204.457838593455</v>
+        <v>2248.582286993329</v>
       </c>
       <c r="E262">
-        <v>4130.553903239042</v>
+        <v>4118.444934848484</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5171,10 +5171,10 @@
         <v>3227.166685201888</v>
       </c>
       <c r="D263">
-        <v>2327.619884907258</v>
+        <v>2309.434667569451</v>
       </c>
       <c r="E263">
-        <v>4241.22423094156</v>
+        <v>4207.819526890097</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5188,10 +5188,10 @@
         <v>3191.400045251264</v>
       </c>
       <c r="D264">
-        <v>2184.156492093934</v>
+        <v>2257.141619509516</v>
       </c>
       <c r="E264">
-        <v>4176.602405849033</v>
+        <v>4142.715743810975</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5205,10 +5205,10 @@
         <v>3068.130517491046</v>
       </c>
       <c r="D265">
-        <v>2080.495804191439</v>
+        <v>2120.179897947033</v>
       </c>
       <c r="E265">
-        <v>3914.703226567169</v>
+        <v>4015.459187746468</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5222,10 +5222,10 @@
         <v>2909.465061152327</v>
       </c>
       <c r="D266">
-        <v>1936.063571932427</v>
+        <v>1951.475746764175</v>
       </c>
       <c r="E266">
-        <v>3860.914163804027</v>
+        <v>3819.498614918432</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5239,10 +5239,10 @@
         <v>2808.423895753756</v>
       </c>
       <c r="D267">
-        <v>1841.138644436007</v>
+        <v>1865.242557139672</v>
       </c>
       <c r="E267">
-        <v>3743.398796784349</v>
+        <v>3803.881485719294</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5256,10 +5256,10 @@
         <v>2985.789451273944</v>
       </c>
       <c r="D268">
-        <v>1960.789348588492</v>
+        <v>2059.966435221373</v>
       </c>
       <c r="E268">
-        <v>3871.947602290431</v>
+        <v>3935.233213754497</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5273,10 +5273,10 @@
         <v>2908.149373729935</v>
       </c>
       <c r="D269">
-        <v>1904.086039506575</v>
+        <v>1936.260613050492</v>
       </c>
       <c r="E269">
-        <v>3791.886071053182</v>
+        <v>3843.28897218048</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5290,10 +5290,10 @@
         <v>3015.438350409877</v>
       </c>
       <c r="D270">
-        <v>2109.996317825502</v>
+        <v>2023.619958955635</v>
       </c>
       <c r="E270">
-        <v>3936.229954657843</v>
+        <v>3939.273569285131</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5307,10 +5307,10 @@
         <v>3033.628179387828</v>
       </c>
       <c r="D271">
-        <v>2009.37737675399</v>
+        <v>2053.731959231713</v>
       </c>
       <c r="E271">
-        <v>3979.185634232977</v>
+        <v>3941.162076651031</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5324,10 +5324,10 @@
         <v>2712.675103787785</v>
       </c>
       <c r="D272">
-        <v>1826.055734253141</v>
+        <v>1832.593355901576</v>
       </c>
       <c r="E272">
-        <v>3599.812572048469</v>
+        <v>3616.88714071721</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5341,10 +5341,10 @@
         <v>2681.620982115504</v>
       </c>
       <c r="D273">
-        <v>1788.282200531578</v>
+        <v>1764.338798267926</v>
       </c>
       <c r="E273">
-        <v>3602.880646363153</v>
+        <v>3576.027792752894</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5358,10 +5358,10 @@
         <v>2530.201561939478</v>
       </c>
       <c r="D274">
-        <v>1638.891115364937</v>
+        <v>1657.308736085875</v>
       </c>
       <c r="E274">
-        <v>3437.842272943455</v>
+        <v>3437.316585630391</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5375,10 +5375,10 @@
         <v>2724.073498833289</v>
       </c>
       <c r="D275">
-        <v>1821.214490448326</v>
+        <v>1834.993302205626</v>
       </c>
       <c r="E275">
-        <v>3596.04497714104</v>
+        <v>3593.031876087496</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5392,10 +5392,10 @@
         <v>2557.606588044103</v>
       </c>
       <c r="D276">
-        <v>1618.247611844941</v>
+        <v>1678.945890526247</v>
       </c>
       <c r="E276">
-        <v>3485.537042291581</v>
+        <v>3515.365119571679</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5409,10 +5409,10 @@
         <v>2673.707774087059</v>
       </c>
       <c r="D277">
-        <v>1798.551975865792</v>
+        <v>1764.260807349187</v>
       </c>
       <c r="E277">
-        <v>3565.417664253685</v>
+        <v>3584.017447450877</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5426,10 +5426,10 @@
         <v>2620.257704410415</v>
       </c>
       <c r="D278">
-        <v>1691.622291917278</v>
+        <v>1717.550342956518</v>
       </c>
       <c r="E278">
-        <v>3503.580858074982</v>
+        <v>3505.846829567117</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5443,10 +5443,10 @@
         <v>2791.295597433157</v>
       </c>
       <c r="D279">
-        <v>1916.788654426934</v>
+        <v>1824.883501024836</v>
       </c>
       <c r="E279">
-        <v>3650.498088723155</v>
+        <v>3657.14257799311</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5460,10 +5460,10 @@
         <v>2794.690910986071</v>
       </c>
       <c r="D280">
-        <v>1769.205709309012</v>
+        <v>1878.705553475766</v>
       </c>
       <c r="E280">
-        <v>3667.376016554661</v>
+        <v>3720.167518609032</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5477,10 +5477,10 @@
         <v>2678.742850440362</v>
       </c>
       <c r="D281">
-        <v>1790.721963824058</v>
+        <v>1761.031684235643</v>
       </c>
       <c r="E281">
-        <v>3607.245019742129</v>
+        <v>3532.742552763349</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5494,10 +5494,10 @@
         <v>2866.061010845472</v>
       </c>
       <c r="D282">
-        <v>1993.227317860179</v>
+        <v>1990.228805496775</v>
       </c>
       <c r="E282">
-        <v>3802.095425032263</v>
+        <v>3717.776212011726</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5511,10 +5511,10 @@
         <v>2635.046733927092</v>
       </c>
       <c r="D283">
-        <v>1746.422257471303</v>
+        <v>1743.97322868651</v>
       </c>
       <c r="E283">
-        <v>3551.266550817896</v>
+        <v>3521.162547104651</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5528,10 +5528,10 @@
         <v>2654.324280626146</v>
       </c>
       <c r="D284">
-        <v>1759.728494659992</v>
+        <v>1806.759639543563</v>
       </c>
       <c r="E284">
-        <v>3505.165350220346</v>
+        <v>3535.921628942644</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5545,10 +5545,10 @@
         <v>2523.609115890758</v>
       </c>
       <c r="D285">
-        <v>1624.107773393092</v>
+        <v>1602.027858193482</v>
       </c>
       <c r="E285">
-        <v>3391.814202364647</v>
+        <v>3401.745363621659</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5562,10 +5562,10 @@
         <v>2676.784700145559</v>
       </c>
       <c r="D286">
-        <v>1741.315784169685</v>
+        <v>1782.385570504008</v>
       </c>
       <c r="E286">
-        <v>3495.264396592685</v>
+        <v>3578.840159623499</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5579,10 +5579,10 @@
         <v>2723.364042461703</v>
       </c>
       <c r="D287">
-        <v>1764.034405013124</v>
+        <v>1886.769779310344</v>
       </c>
       <c r="E287">
-        <v>3656.611012239598</v>
+        <v>3606.608171510268</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5596,10 +5596,10 @@
         <v>2676.843444343551</v>
       </c>
       <c r="D288">
-        <v>1827.750992176697</v>
+        <v>1830.172128367716</v>
       </c>
       <c r="E288">
-        <v>3557.388657905517</v>
+        <v>3549.729694683122</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5613,10 +5613,10 @@
         <v>2915.779042438423</v>
       </c>
       <c r="D289">
-        <v>1991.254765160376</v>
+        <v>2035.552743863339</v>
       </c>
       <c r="E289">
-        <v>3828.203977634471</v>
+        <v>3829.865341999247</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5630,10 +5630,10 @@
         <v>2694.306062989705</v>
       </c>
       <c r="D290">
-        <v>1849.951632813349</v>
+        <v>1796.869727149023</v>
       </c>
       <c r="E290">
-        <v>3622.243158933476</v>
+        <v>3603.515313199782</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5647,10 +5647,10 @@
         <v>2683.492842884059</v>
       </c>
       <c r="D291">
-        <v>1830.259086313463</v>
+        <v>1800.605804724114</v>
       </c>
       <c r="E291">
-        <v>3567.786232284543</v>
+        <v>3611.087900006097</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5664,10 +5664,10 @@
         <v>2501.808618642208</v>
       </c>
       <c r="D292">
-        <v>1635.392748427235</v>
+        <v>1589.082530485117</v>
       </c>
       <c r="E292">
-        <v>3364.423465918104</v>
+        <v>3339.686466820153</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5681,10 +5681,10 @@
         <v>2600.303588753989</v>
       </c>
       <c r="D293">
-        <v>1656.381435592757</v>
+        <v>1731.993736556805</v>
       </c>
       <c r="E293">
-        <v>3531.722272215859</v>
+        <v>3521.120411025906</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5698,10 +5698,10 @@
         <v>2598.771373342413</v>
       </c>
       <c r="D294">
-        <v>1667.292107548473</v>
+        <v>1747.544339713301</v>
       </c>
       <c r="E294">
-        <v>3448.964801669791</v>
+        <v>3512.291888830234</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5715,10 +5715,10 @@
         <v>2518.045984548499</v>
       </c>
       <c r="D295">
-        <v>1683.280261656625</v>
+        <v>1614.922816040062</v>
       </c>
       <c r="E295">
-        <v>3407.658763857106</v>
+        <v>3423.656804128114</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5732,10 +5732,10 @@
         <v>2745.639893743472</v>
       </c>
       <c r="D296">
-        <v>1804.299513032163</v>
+        <v>1860.931602008421</v>
       </c>
       <c r="E296">
-        <v>3603.479213370888</v>
+        <v>3663.772529035306</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5749,10 +5749,10 @@
         <v>2542.758820848155</v>
       </c>
       <c r="D297">
-        <v>1632.533634297949</v>
+        <v>1642.090740876507</v>
       </c>
       <c r="E297">
-        <v>3472.334979953658</v>
+        <v>3462.594832617535</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5766,10 +5766,10 @@
         <v>2574.681907491946</v>
       </c>
       <c r="D298">
-        <v>1663.795108989392</v>
+        <v>1670.550503450051</v>
       </c>
       <c r="E298">
-        <v>3437.990994339973</v>
+        <v>3489.34889991664</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5783,10 +5783,10 @@
         <v>2440.840364417534</v>
       </c>
       <c r="D299">
-        <v>1491.949093883573</v>
+        <v>1604.403313421341</v>
       </c>
       <c r="E299">
-        <v>3353.748750699525</v>
+        <v>3385.178126132589</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5800,10 +5800,10 @@
         <v>2570.499860865859</v>
       </c>
       <c r="D300">
-        <v>1696.666953713514</v>
+        <v>1664.688707022447</v>
       </c>
       <c r="E300">
-        <v>3501.055783364566</v>
+        <v>3437.290644555773</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5817,10 +5817,10 @@
         <v>2576.739992145268</v>
       </c>
       <c r="D301">
-        <v>1679.647619004402</v>
+        <v>1720.024086518521</v>
       </c>
       <c r="E301">
-        <v>3438.879550156046</v>
+        <v>3444.765917233683</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5834,10 +5834,10 @@
         <v>2493.627947952636</v>
       </c>
       <c r="D302">
-        <v>1597.103224870461</v>
+        <v>1578.434260894708</v>
       </c>
       <c r="E302">
-        <v>3394.491583781085</v>
+        <v>3371.927540360184</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5851,10 +5851,10 @@
         <v>2729.098431533841</v>
       </c>
       <c r="D303">
-        <v>1838.290377250694</v>
+        <v>1910.59660785955</v>
       </c>
       <c r="E303">
-        <v>3641.960213282271</v>
+        <v>3600.647330210403</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5868,10 +5868,10 @@
         <v>2552.284471700239</v>
       </c>
       <c r="D304">
-        <v>1657.524042027392</v>
+        <v>1569.449159485271</v>
       </c>
       <c r="E304">
-        <v>3495.196488374629</v>
+        <v>3455.988172153995</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5885,10 +5885,10 @@
         <v>2613.6296660146</v>
       </c>
       <c r="D305">
-        <v>1744.581602199285</v>
+        <v>1732.436899815457</v>
       </c>
       <c r="E305">
-        <v>3513.527694960168</v>
+        <v>3521.929654848446</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5902,10 +5902,10 @@
         <v>2489.697712252718</v>
       </c>
       <c r="D306">
-        <v>1569.733373339155</v>
+        <v>1598.683989635333</v>
       </c>
       <c r="E306">
-        <v>3370.421879187283</v>
+        <v>3384.873910413209</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5919,10 +5919,10 @@
         <v>2601.650788285319</v>
       </c>
       <c r="D307">
-        <v>1715.74865853078</v>
+        <v>1681.848011242089</v>
       </c>
       <c r="E307">
-        <v>3471.065827461401</v>
+        <v>3491.566348896824</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5936,10 +5936,10 @@
         <v>2582.04207403434</v>
       </c>
       <c r="D308">
-        <v>1728.245323583108</v>
+        <v>1644.283975732283</v>
       </c>
       <c r="E308">
-        <v>3501.819182095419</v>
+        <v>3494.830968112177</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5953,10 +5953,10 @@
         <v>2497.306035516699</v>
       </c>
       <c r="D309">
-        <v>1616.776668906266</v>
+        <v>1562.28963518177</v>
       </c>
       <c r="E309">
-        <v>3400.960184507527</v>
+        <v>3367.608306756195</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5970,10 +5970,10 @@
         <v>2771.267455500399</v>
       </c>
       <c r="D310">
-        <v>1912.571375875068</v>
+        <v>1840.212104319279</v>
       </c>
       <c r="E310">
-        <v>3642.152799695576</v>
+        <v>3667.13579242943</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5987,10 +5987,10 @@
         <v>2654.703658926235</v>
       </c>
       <c r="D311">
-        <v>1762.668951954474</v>
+        <v>1737.64861738774</v>
       </c>
       <c r="E311">
-        <v>3483.600170725511</v>
+        <v>3576.88735135355</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -6004,10 +6004,10 @@
         <v>2754.576201816423</v>
       </c>
       <c r="D312">
-        <v>1861.713183681126</v>
+        <v>1821.643775071106</v>
       </c>
       <c r="E312">
-        <v>3731.062868271679</v>
+        <v>3665.627465769445</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -6021,10 +6021,10 @@
         <v>2613.937613707052</v>
       </c>
       <c r="D313">
-        <v>1711.36276065291</v>
+        <v>1708.089516052438</v>
       </c>
       <c r="E313">
-        <v>3597.004756970847</v>
+        <v>3448.463007150672</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -6038,10 +6038,10 @@
         <v>2658.139349730248</v>
       </c>
       <c r="D314">
-        <v>1823.080935461433</v>
+        <v>1749.68040520523</v>
       </c>
       <c r="E314">
-        <v>3586.703439626015</v>
+        <v>3603.345162930213</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -6055,10 +6055,10 @@
         <v>2562.2629869856</v>
       </c>
       <c r="D315">
-        <v>1715.945480455636</v>
+        <v>1643.665955177604</v>
       </c>
       <c r="E315">
-        <v>3503.27330605955</v>
+        <v>3425.549895634886</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6072,10 +6072,10 @@
         <v>2442.71353806365</v>
       </c>
       <c r="D316">
-        <v>1466.362393131877</v>
+        <v>1633.184183011959</v>
       </c>
       <c r="E316">
-        <v>3313.405522692597</v>
+        <v>3379.233887906736</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -6089,10 +6089,10 @@
         <v>2745.13419130347</v>
       </c>
       <c r="D317">
-        <v>1874.908143203068</v>
+        <v>1830.501346532237</v>
       </c>
       <c r="E317">
-        <v>3588.383907319064</v>
+        <v>3609.685982212138</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -6106,10 +6106,10 @@
         <v>2701.564301680634</v>
       </c>
       <c r="D318">
-        <v>1776.506748180283</v>
+        <v>1744.768569662899</v>
       </c>
       <c r="E318">
-        <v>3599.945508763431</v>
+        <v>3611.431370964227</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -6123,10 +6123,10 @@
         <v>2875.098427446637</v>
       </c>
       <c r="D319">
-        <v>2043.207196940316</v>
+        <v>1963.864091784133</v>
       </c>
       <c r="E319">
-        <v>3782.873720473221</v>
+        <v>3765.701999522771</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6140,10 +6140,10 @@
         <v>2772.175695383269</v>
       </c>
       <c r="D320">
-        <v>1884.529385939951</v>
+        <v>1880.157388985738</v>
       </c>
       <c r="E320">
-        <v>3687.899837480425</v>
+        <v>3664.090840248511</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -6157,10 +6157,10 @@
         <v>2807.329447130614</v>
       </c>
       <c r="D321">
-        <v>1973.880378618189</v>
+        <v>1947.681217200666</v>
       </c>
       <c r="E321">
-        <v>3732.551956059139</v>
+        <v>3710.672296306034</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -6174,10 +6174,10 @@
         <v>2668.711510274105</v>
       </c>
       <c r="D322">
-        <v>1696.146013572562</v>
+        <v>1770.963058684258</v>
       </c>
       <c r="E322">
-        <v>3593.020913534916</v>
+        <v>3593.719832309422</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6191,10 +6191,10 @@
         <v>2492.271459502688</v>
       </c>
       <c r="D323">
-        <v>1597.896635884969</v>
+        <v>1581.07341979307</v>
       </c>
       <c r="E323">
-        <v>3366.057258007016</v>
+        <v>3468.096420559465</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -6208,10 +6208,10 @@
         <v>2737.109890490864</v>
       </c>
       <c r="D324">
-        <v>1867.455726072204</v>
+        <v>1844.671711182112</v>
       </c>
       <c r="E324">
-        <v>3621.30977131779</v>
+        <v>3622.944381433722</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6225,10 +6225,10 @@
         <v>2643.715905207433</v>
       </c>
       <c r="D325">
-        <v>1754.244260384312</v>
+        <v>1672.133248800145</v>
       </c>
       <c r="E325">
-        <v>3590.401623255061</v>
+        <v>3517.573072503869</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6242,10 +6242,10 @@
         <v>2783.25187580451</v>
       </c>
       <c r="D326">
-        <v>1894.580411327808</v>
+        <v>1874.803346823925</v>
       </c>
       <c r="E326">
-        <v>3639.680292432156</v>
+        <v>3700.167314883874</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6259,10 +6259,10 @@
         <v>2671.775506001909</v>
       </c>
       <c r="D327">
-        <v>1764.182526840116</v>
+        <v>1742.90316446776</v>
       </c>
       <c r="E327">
-        <v>3553.021172591076</v>
+        <v>3530.530526470201</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6276,10 +6276,10 @@
         <v>2725.541039739038</v>
       </c>
       <c r="D328">
-        <v>1764.781585803835</v>
+        <v>1846.015788974453</v>
       </c>
       <c r="E328">
-        <v>3622.26618197477</v>
+        <v>3641.120619806287</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6293,10 +6293,10 @@
         <v>2620.396556481418</v>
       </c>
       <c r="D329">
-        <v>1767.5367681962</v>
+        <v>1711.988170400303</v>
       </c>
       <c r="E329">
-        <v>3551.200150605496</v>
+        <v>3512.404195447835</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6310,10 +6310,10 @@
         <v>2470.186376923518</v>
       </c>
       <c r="D330">
-        <v>1644.638759534918</v>
+        <v>1682.031502055323</v>
       </c>
       <c r="E330">
-        <v>3428.481729640648</v>
+        <v>3318.130858976887</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6327,10 +6327,10 @@
         <v>2718.253040929337</v>
       </c>
       <c r="D331">
-        <v>1854.256794399202</v>
+        <v>1820.05233702849</v>
       </c>
       <c r="E331">
-        <v>3616.39015141935</v>
+        <v>3638.475561648097</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6344,10 +6344,10 @@
         <v>2609.666551818221</v>
       </c>
       <c r="D332">
-        <v>1703.518629289212</v>
+        <v>1672.125028429895</v>
       </c>
       <c r="E332">
-        <v>3499.270321100698</v>
+        <v>3486.342945939696</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6361,10 +6361,10 @@
         <v>2735.141646195969</v>
       </c>
       <c r="D333">
-        <v>1772.698498187783</v>
+        <v>1769.079667163613</v>
       </c>
       <c r="E333">
-        <v>3571.815102787137</v>
+        <v>3653.078571067694</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6378,10 +6378,10 @@
         <v>2627.800391593551</v>
       </c>
       <c r="D334">
-        <v>1720.904808741211</v>
+        <v>1704.784950122646</v>
       </c>
       <c r="E334">
-        <v>3501.697952034204</v>
+        <v>3528.826637675326</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6395,10 +6395,10 @@
         <v>2700.317938158822</v>
       </c>
       <c r="D335">
-        <v>1794.892594448154</v>
+        <v>1810.968775602933</v>
       </c>
       <c r="E335">
-        <v>3633.060502315872</v>
+        <v>3583.588986345351</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6412,10 +6412,10 @@
         <v>2607.620255861676</v>
       </c>
       <c r="D336">
-        <v>1755.62239379479</v>
+        <v>1714.027318094693</v>
       </c>
       <c r="E336">
-        <v>3515.599882388027</v>
+        <v>3500.432447472888</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6429,10 +6429,10 @@
         <v>2445.623650281132</v>
       </c>
       <c r="D337">
-        <v>1486.562796799888</v>
+        <v>1556.884720210521</v>
       </c>
       <c r="E337">
-        <v>3314.613451840202</v>
+        <v>3318.033955070142</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6446,10 +6446,10 @@
         <v>2663.426563776258</v>
       </c>
       <c r="D338">
-        <v>1811.847225750959</v>
+        <v>1740.693349139753</v>
       </c>
       <c r="E338">
-        <v>3545.944418959917</v>
+        <v>3564.023412965228</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6463,10 +6463,10 @@
         <v>2535.74151969425</v>
       </c>
       <c r="D339">
-        <v>1678.263057973937</v>
+        <v>1703.976292440941</v>
       </c>
       <c r="E339">
-        <v>3341.867122455269</v>
+        <v>3447.757428963042</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6480,10 +6480,10 @@
         <v>2680.891706043255</v>
       </c>
       <c r="D340">
-        <v>1748.175882258547</v>
+        <v>1813.294882698677</v>
       </c>
       <c r="E340">
-        <v>3571.503866720114</v>
+        <v>3551.579840826947</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6497,10 +6497,10 @@
         <v>2631.692626580143</v>
       </c>
       <c r="D341">
-        <v>1697.128583255233</v>
+        <v>1734.96603421389</v>
       </c>
       <c r="E341">
-        <v>3519.70599784599</v>
+        <v>3475.689534114437</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6514,10 +6514,10 @@
         <v>2766.415999592123</v>
       </c>
       <c r="D342">
-        <v>1884.659155995353</v>
+        <v>1896.649216882259</v>
       </c>
       <c r="E342">
-        <v>3745.778430691457</v>
+        <v>3704.621500748025</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6531,10 +6531,10 @@
         <v>2697.114915211641</v>
       </c>
       <c r="D343">
-        <v>1929.540106391441</v>
+        <v>1814.280447133598</v>
       </c>
       <c r="E343">
-        <v>3631.545533652314</v>
+        <v>3540.598780875874</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6548,10 +6548,10 @@
         <v>2502.666737453432</v>
       </c>
       <c r="D344">
-        <v>1588.331970188218</v>
+        <v>1735.043380634513</v>
       </c>
       <c r="E344">
-        <v>3417.72968884966</v>
+        <v>3389.282835052117</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6565,10 +6565,10 @@
         <v>2657.139855554465</v>
       </c>
       <c r="D345">
-        <v>1708.092972037501</v>
+        <v>1765.427577249056</v>
       </c>
       <c r="E345">
-        <v>3563.300036462667</v>
+        <v>3543.907586766439</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6582,10 +6582,10 @@
         <v>2486.196439544105</v>
       </c>
       <c r="D346">
-        <v>1583.345797160189</v>
+        <v>1608.612384428803</v>
       </c>
       <c r="E346">
-        <v>3400.30379197205</v>
+        <v>3368.689832656391</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6599,10 +6599,10 @@
         <v>2646.829771000914</v>
       </c>
       <c r="D347">
-        <v>1771.284987635414</v>
+        <v>1730.667779578502</v>
       </c>
       <c r="E347">
-        <v>3604.670308245675</v>
+        <v>3620.486564645486</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6616,10 +6616,10 @@
         <v>2672.715429313533</v>
       </c>
       <c r="D348">
-        <v>1766.731130505115</v>
+        <v>1782.785715158861</v>
       </c>
       <c r="E348">
-        <v>3561.643607859595</v>
+        <v>3593.093150069891</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6633,10 +6633,10 @@
         <v>2906.485698131321</v>
       </c>
       <c r="D349">
-        <v>1934.25686663492</v>
+        <v>2018.344004040633</v>
       </c>
       <c r="E349">
-        <v>3749.619701305067</v>
+        <v>3834.359376477131</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6650,10 +6650,10 @@
         <v>2916.101727710933</v>
       </c>
       <c r="D350">
-        <v>2015.269784884609</v>
+        <v>2010.745140513033</v>
       </c>
       <c r="E350">
-        <v>3721.674943670596</v>
+        <v>3820.681125847588</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6667,10 +6667,10 @@
         <v>2755.062628933293</v>
       </c>
       <c r="D351">
-        <v>1866.851438532555</v>
+        <v>1862.465259321029</v>
       </c>
       <c r="E351">
-        <v>3661.804011996409</v>
+        <v>3559.522979687045</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6684,10 +6684,10 @@
         <v>2899.310307195731</v>
       </c>
       <c r="D352">
-        <v>1987.957068525203</v>
+        <v>1992.380239724462</v>
       </c>
       <c r="E352">
-        <v>3767.58028189562</v>
+        <v>3795.062830571796</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6701,10 +6701,10 @@
         <v>2692.744445931236</v>
       </c>
       <c r="D353">
-        <v>1843.713292400616</v>
+        <v>1783.29005353367</v>
       </c>
       <c r="E353">
-        <v>3557.974358186018</v>
+        <v>3549.705123879899</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6718,10 +6718,10 @@
         <v>2808.799466975531</v>
       </c>
       <c r="D354">
-        <v>1845.603098929644</v>
+        <v>1954.760007007241</v>
       </c>
       <c r="E354">
-        <v>3707.336337243521</v>
+        <v>3681.274580680999</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6735,10 +6735,10 @@
         <v>2791.056265824102</v>
       </c>
       <c r="D355">
-        <v>1892.754135741402</v>
+        <v>1957.654433551104</v>
       </c>
       <c r="E355">
-        <v>3659.02352029328</v>
+        <v>3646.519076444235</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6752,10 +6752,10 @@
         <v>2988.995262285559</v>
       </c>
       <c r="D356">
-        <v>2076.18397975459</v>
+        <v>2099.324910442446</v>
       </c>
       <c r="E356">
-        <v>3827.777812790416</v>
+        <v>3852.178667268749</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6769,10 +6769,10 @@
         <v>2979.893295556046</v>
       </c>
       <c r="D357">
-        <v>2107.761591444005</v>
+        <v>2108.106491344971</v>
       </c>
       <c r="E357">
-        <v>3871.733519431398</v>
+        <v>3836.437309892175</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6786,10 +6786,10 @@
         <v>2823.820094635417</v>
       </c>
       <c r="D358">
-        <v>2004.214924992827</v>
+        <v>1959.760901802894</v>
       </c>
       <c r="E358">
-        <v>3785.527906155431</v>
+        <v>3713.268445407514</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6803,10 +6803,10 @@
         <v>2991.264976488848</v>
       </c>
       <c r="D359">
-        <v>2039.554719658292</v>
+        <v>2156.318635844048</v>
       </c>
       <c r="E359">
-        <v>3830.787574720656</v>
+        <v>3901.60060329393</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6820,10 +6820,10 @@
         <v>2807.70025316369</v>
       </c>
       <c r="D360">
-        <v>1899.620418105036</v>
+        <v>1913.750759295042</v>
       </c>
       <c r="E360">
-        <v>3750.19779649763</v>
+        <v>3672.882875568089</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6837,10 +6837,10 @@
         <v>2925.218725090952</v>
       </c>
       <c r="D361">
-        <v>1987.470385672222</v>
+        <v>2005.555137400323</v>
       </c>
       <c r="E361">
-        <v>3750.992331728256</v>
+        <v>3787.332446515283</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6854,10 +6854,10 @@
         <v>2791.105628556902</v>
       </c>
       <c r="D362">
-        <v>1861.793769634639</v>
+        <v>1896.635515456365</v>
       </c>
       <c r="E362">
-        <v>3679.536688701257</v>
+        <v>3669.105401843955</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6871,10 +6871,10 @@
         <v>3107.732271739924</v>
       </c>
       <c r="D363">
-        <v>2202.563320983031</v>
+        <v>2235.729711399141</v>
       </c>
       <c r="E363">
-        <v>3902.717254494079</v>
+        <v>4019.269647489652</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6888,10 +6888,10 @@
         <v>3165.980927175927</v>
       </c>
       <c r="D364">
-        <v>2272.634938370751</v>
+        <v>2329.011976875584</v>
       </c>
       <c r="E364">
-        <v>4037.826282445122</v>
+        <v>4098.620532024365</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6905,10 +6905,10 @@
         <v>3023.684715603961</v>
       </c>
       <c r="D365">
-        <v>2160.136803647666</v>
+        <v>2166.912526942171</v>
       </c>
       <c r="E365">
-        <v>3853.942674660375</v>
+        <v>3968.830748923776</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6922,10 +6922,10 @@
         <v>3067.884012644932</v>
       </c>
       <c r="D366">
-        <v>2150.034372028196</v>
+        <v>2155.581226368414</v>
       </c>
       <c r="E366">
-        <v>4018.047872209767</v>
+        <v>3901.114969444066</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6939,10 +6939,10 @@
         <v>2885.500707310452</v>
       </c>
       <c r="D367">
-        <v>2002.902627578223</v>
+        <v>2016.780349120058</v>
       </c>
       <c r="E367">
-        <v>3739.410786744931</v>
+        <v>3718.189310459178</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6956,10 +6956,10 @@
         <v>2916.602366441592</v>
       </c>
       <c r="D368">
-        <v>1988.900988589503</v>
+        <v>2025.1046728649</v>
       </c>
       <c r="E368">
-        <v>3772.519266254468</v>
+        <v>3816.084998545357</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6973,10 +6973,10 @@
         <v>2670.317062345699</v>
       </c>
       <c r="D369">
-        <v>1772.969698748725</v>
+        <v>1720.027140086309</v>
       </c>
       <c r="E369">
-        <v>3509.212777249435</v>
+        <v>3522.48585824833</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6990,10 +6990,10 @@
         <v>2951.722655449946</v>
       </c>
       <c r="D370">
-        <v>2058.701186280776</v>
+        <v>2099.565246085919</v>
       </c>
       <c r="E370">
-        <v>3841.656902642567</v>
+        <v>3800.651119056413</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -7007,10 +7007,10 @@
         <v>3002.455434831187</v>
       </c>
       <c r="D371">
-        <v>2090.390451854651</v>
+        <v>2122.997013940976</v>
       </c>
       <c r="E371">
-        <v>3871.277852265448</v>
+        <v>3826.585273437461</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -7024,10 +7024,10 @@
         <v>2867.532157077114</v>
       </c>
       <c r="D372">
-        <v>1974.500034288305</v>
+        <v>1985.778245846942</v>
       </c>
       <c r="E372">
-        <v>3769.086058597466</v>
+        <v>3736.779564194364</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -7041,10 +7041,10 @@
         <v>2926.739896661525</v>
       </c>
       <c r="D373">
-        <v>2055.501024892555</v>
+        <v>2024.335172596983</v>
       </c>
       <c r="E373">
-        <v>3758.229748132234</v>
+        <v>3805.174724974946</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -7058,10 +7058,10 @@
         <v>2761.783167623713</v>
       </c>
       <c r="D374">
-        <v>1896.688167218504</v>
+        <v>1891.704612168738</v>
       </c>
       <c r="E374">
-        <v>3646.186232248272</v>
+        <v>3576.995527549897</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -7075,10 +7075,10 @@
         <v>2799.776132607639</v>
       </c>
       <c r="D375">
-        <v>1946.90811283874</v>
+        <v>1948.863584097245</v>
       </c>
       <c r="E375">
-        <v>3679.933411889518</v>
+        <v>3755.022969997511</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7092,10 +7092,10 @@
         <v>2530.768264080845</v>
       </c>
       <c r="D376">
-        <v>1656.828225702741</v>
+        <v>1703.378710648782</v>
       </c>
       <c r="E376">
-        <v>3409.578734815068</v>
+        <v>3415.544407171819</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -7109,10 +7109,10 @@
         <v>2749.945925256036</v>
       </c>
       <c r="D377">
-        <v>1915.436859316224</v>
+        <v>1925.583095856839</v>
       </c>
       <c r="E377">
-        <v>3645.060225439634</v>
+        <v>3662.579939574402</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -7126,10 +7126,10 @@
         <v>2714.897457128181</v>
       </c>
       <c r="D378">
-        <v>1873.637622953217</v>
+        <v>1853.684052160735</v>
       </c>
       <c r="E378">
-        <v>3575.665430208127</v>
+        <v>3602.665306161188</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7143,10 +7143,10 @@
         <v>2508.763717275829</v>
       </c>
       <c r="D379">
-        <v>1673.810623266282</v>
+        <v>1656.720216329116</v>
       </c>
       <c r="E379">
-        <v>3399.00617051915</v>
+        <v>3323.628916650609</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -7160,10 +7160,10 @@
         <v>2546.724814151266</v>
       </c>
       <c r="D380">
-        <v>1669.597928974576</v>
+        <v>1671.695128579468</v>
       </c>
       <c r="E380">
-        <v>3409.505296944599</v>
+        <v>3381.746484746778</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -7177,10 +7177,10 @@
         <v>2416.046853154666</v>
       </c>
       <c r="D381">
-        <v>1530.39519825564</v>
+        <v>1558.69623493842</v>
       </c>
       <c r="E381">
-        <v>3291.568037899211</v>
+        <v>3271.343775902272</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7194,10 +7194,10 @@
         <v>2514.681346425516</v>
       </c>
       <c r="D382">
-        <v>1616.078602442851</v>
+        <v>1650.714517866046</v>
       </c>
       <c r="E382">
-        <v>3380.942456181567</v>
+        <v>3372.221362223972</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7211,10 +7211,10 @@
         <v>2294.02514989246</v>
       </c>
       <c r="D383">
-        <v>1382.328843026551</v>
+        <v>1437.387403199582</v>
       </c>
       <c r="E383">
-        <v>3137.856816339517</v>
+        <v>3130.979854961663</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7228,10 +7228,10 @@
         <v>2534.083485310805</v>
       </c>
       <c r="D384">
-        <v>1671.848797738803</v>
+        <v>1604.425411251446</v>
       </c>
       <c r="E384">
-        <v>3345.23281249669</v>
+        <v>3490.360781031657</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7245,10 +7245,10 @@
         <v>2513.46841235478</v>
       </c>
       <c r="D385">
-        <v>1653.067581651466</v>
+        <v>1653.088360857879</v>
       </c>
       <c r="E385">
-        <v>3355.231505192938</v>
+        <v>3399.249916350286</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7262,10 +7262,10 @@
         <v>2350.785099620075</v>
       </c>
       <c r="D386">
-        <v>1503.118643686223</v>
+        <v>1450.228700431225</v>
       </c>
       <c r="E386">
-        <v>3221.341771457467</v>
+        <v>3252.937306630047</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7279,10 +7279,10 @@
         <v>2475.39433138995</v>
       </c>
       <c r="D387">
-        <v>1624.186480596323</v>
+        <v>1559.847938185589</v>
       </c>
       <c r="E387">
-        <v>3306.857246613638</v>
+        <v>3388.553013454547</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7296,10 +7296,10 @@
         <v>2450.142010722806</v>
       </c>
       <c r="D388">
-        <v>1510.522517446614</v>
+        <v>1500.776776422062</v>
       </c>
       <c r="E388">
-        <v>3232.941044640778</v>
+        <v>3305.975353812113</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7313,10 +7313,10 @@
         <v>2627.324715769023</v>
       </c>
       <c r="D389">
-        <v>1799.118136394556</v>
+        <v>1789.079561880061</v>
       </c>
       <c r="E389">
-        <v>3591.412963628583</v>
+        <v>3498.618847105538</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7330,10 +7330,10 @@
         <v>2430.06443162805</v>
       </c>
       <c r="D390">
-        <v>1544.490614048483</v>
+        <v>1529.229230053734</v>
       </c>
       <c r="E390">
-        <v>3318.624691919038</v>
+        <v>3275.686995735957</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7347,10 +7347,10 @@
         <v>2651.618613971155</v>
       </c>
       <c r="D391">
-        <v>1746.817900935838</v>
+        <v>1763.454582969788</v>
       </c>
       <c r="E391">
-        <v>3532.344857763686</v>
+        <v>3487.575062787857</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7364,10 +7364,10 @@
         <v>2614.98631947767</v>
       </c>
       <c r="D392">
-        <v>1731.556861913204</v>
+        <v>1777.582943272836</v>
       </c>
       <c r="E392">
-        <v>3465.604857470919</v>
+        <v>3407.466464719724</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7381,10 +7381,10 @@
         <v>2476.397139420144</v>
       </c>
       <c r="D393">
-        <v>1612.363606162778</v>
+        <v>1531.628749641169</v>
       </c>
       <c r="E393">
-        <v>3385.76770113141</v>
+        <v>3383.02497703998</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7398,10 +7398,10 @@
         <v>2665.116909030173</v>
       </c>
       <c r="D394">
-        <v>1789.768389737485</v>
+        <v>1809.049048298728</v>
       </c>
       <c r="E394">
-        <v>3545.027910517597</v>
+        <v>3469.416495234804</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7415,10 +7415,10 @@
         <v>2707.826501940804</v>
       </c>
       <c r="D395">
-        <v>1856.307471195409</v>
+        <v>1890.962417917138</v>
       </c>
       <c r="E395">
-        <v>3596.24235222722</v>
+        <v>3580.273315793388</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7432,10 +7432,10 @@
         <v>2915.130162833454</v>
       </c>
       <c r="D396">
-        <v>1991.846085643535</v>
+        <v>2039.822109752753</v>
       </c>
       <c r="E396">
-        <v>3789.217043066895</v>
+        <v>3803.39463310013</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7449,10 +7449,10 @@
         <v>2696.011200847793</v>
       </c>
       <c r="D397">
-        <v>1797.664061248759</v>
+        <v>1828.867190616596</v>
       </c>
       <c r="E397">
-        <v>3590.903342700909</v>
+        <v>3461.802775926378</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7466,10 +7466,10 @@
         <v>2864.145610203284</v>
       </c>
       <c r="D398">
-        <v>2012.74581323509</v>
+        <v>1990.749772863251</v>
       </c>
       <c r="E398">
-        <v>3718.027506175857</v>
+        <v>3749.740208479077</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7483,10 +7483,10 @@
         <v>2777.971851144228</v>
       </c>
       <c r="D399">
-        <v>1915.361948692477</v>
+        <v>1895.433480495147</v>
       </c>
       <c r="E399">
-        <v>3625.911839915153</v>
+        <v>3620.596967328593</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7500,10 +7500,10 @@
         <v>2616.682102574993</v>
       </c>
       <c r="D400">
-        <v>1764.80098792177</v>
+        <v>1697.317018854506</v>
       </c>
       <c r="E400">
-        <v>3401.322069319389</v>
+        <v>3494.796544896692</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7517,10 +7517,10 @@
         <v>2809.595922499661</v>
       </c>
       <c r="D401">
-        <v>1906.72601550355</v>
+        <v>1888.51161204127</v>
       </c>
       <c r="E401">
-        <v>3716.936391596593</v>
+        <v>3618.96527880604</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7534,10 +7534,10 @@
         <v>2870.777884494631</v>
       </c>
       <c r="D402">
-        <v>2008.879316588056</v>
+        <v>2024.960138764342</v>
       </c>
       <c r="E402">
-        <v>3753.091188335661</v>
+        <v>3783.694675232369</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7551,10 +7551,10 @@
         <v>3100.160967722229</v>
       </c>
       <c r="D403">
-        <v>2185.371871575731</v>
+        <v>2238.943383240347</v>
       </c>
       <c r="E403">
-        <v>4025.826818934211</v>
+        <v>3971.026831090372</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7568,10 +7568,10 @@
         <v>2901.803677764804</v>
       </c>
       <c r="D404">
-        <v>2026.916342264138</v>
+        <v>2031.784667025037</v>
       </c>
       <c r="E404">
-        <v>3739.023032649336</v>
+        <v>3759.435420073708</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7585,10 +7585,10 @@
         <v>3081.048797276212</v>
       </c>
       <c r="D405">
-        <v>2208.6512117303</v>
+        <v>2257.532282989608</v>
       </c>
       <c r="E405">
-        <v>3929.83814276947</v>
+        <v>3907.581038892896</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7602,10 +7602,10 @@
         <v>2979.524051147432</v>
       </c>
       <c r="D406">
-        <v>2050.602731292363</v>
+        <v>2110.28135547253</v>
       </c>
       <c r="E406">
-        <v>3927.811012684321</v>
+        <v>3875.40502978206</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7619,10 +7619,10 @@
         <v>2759.836201116873</v>
       </c>
       <c r="D407">
-        <v>1879.452385329469</v>
+        <v>1864.671947526054</v>
       </c>
       <c r="E407">
-        <v>3591.118865473985</v>
+        <v>3654.621688169762</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7636,10 +7636,10 @@
         <v>2853.588322851005</v>
       </c>
       <c r="D408">
-        <v>1964.163231914511</v>
+        <v>1977.370275134575</v>
       </c>
       <c r="E408">
-        <v>3737.08300313937</v>
+        <v>3734.112002449491</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7653,10 +7653,10 @@
         <v>2804.475662966282</v>
       </c>
       <c r="D409">
-        <v>1965.02501266307</v>
+        <v>1910.048920884485</v>
       </c>
       <c r="E409">
-        <v>3727.973506741348</v>
+        <v>3641.094561433727</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7670,10 +7670,10 @@
         <v>2953.748364724758</v>
       </c>
       <c r="D410">
-        <v>2099.847212405244</v>
+        <v>2102.271634904794</v>
       </c>
       <c r="E410">
-        <v>3822.256299186516</v>
+        <v>3857.233903500372</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7687,10 +7687,10 @@
         <v>2729.288043874122</v>
       </c>
       <c r="D411">
-        <v>1807.425732229956</v>
+        <v>1855.62069660021</v>
       </c>
       <c r="E411">
-        <v>3592.409391284469</v>
+        <v>3553.888814637949</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7704,10 +7704,10 @@
         <v>2923.809670968875</v>
       </c>
       <c r="D412">
-        <v>2010.958358792282</v>
+        <v>2076.529722584578</v>
       </c>
       <c r="E412">
-        <v>3809.037115205811</v>
+        <v>3773.688782918402</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7721,10 +7721,10 @@
         <v>2841.68564283127</v>
       </c>
       <c r="D413">
-        <v>1925.515637123402</v>
+        <v>2006.952085697804</v>
       </c>
       <c r="E413">
-        <v>3685.063164356765</v>
+        <v>3708.53536423484</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7738,10 +7738,10 @@
         <v>2616.018764146176</v>
       </c>
       <c r="D414">
-        <v>1747.90008883658</v>
+        <v>1759.435765103705</v>
       </c>
       <c r="E414">
-        <v>3453.566232842092</v>
+        <v>3486.632715997452</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7755,10 +7755,10 @@
         <v>2682.728928337481</v>
       </c>
       <c r="D415">
-        <v>1820.856490284139</v>
+        <v>1821.061643104478</v>
       </c>
       <c r="E415">
-        <v>3546.858876549116</v>
+        <v>3549.498600700541</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7772,10 +7772,10 @@
         <v>2618.863291595458</v>
       </c>
       <c r="D416">
-        <v>1631.582399731037</v>
+        <v>1785.854208499002</v>
       </c>
       <c r="E416">
-        <v>3527.442431001341</v>
+        <v>3470.093590330489</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7789,10 +7789,10 @@
         <v>2795.262020472541</v>
       </c>
       <c r="D417">
-        <v>1969.408520746394</v>
+        <v>1904.587592669095</v>
       </c>
       <c r="E417">
-        <v>3650.574138087848</v>
+        <v>3613.556724385814</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7806,10 +7806,10 @@
         <v>2635.542068658464</v>
       </c>
       <c r="D418">
-        <v>1769.365928094568</v>
+        <v>1733.632421045747</v>
       </c>
       <c r="E418">
-        <v>3507.115325350903</v>
+        <v>3486.165685351605</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7823,10 +7823,10 @@
         <v>2893.632211771395</v>
       </c>
       <c r="D419">
-        <v>1994.698455226075</v>
+        <v>2017.901306343862</v>
       </c>
       <c r="E419">
-        <v>3740.481134766935</v>
+        <v>3763.289089483696</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7840,10 +7840,10 @@
         <v>2832.90497587172</v>
       </c>
       <c r="D420">
-        <v>1982.290186851274</v>
+        <v>1998.280895696786</v>
       </c>
       <c r="E420">
-        <v>3719.900371198109</v>
+        <v>3747.352217924033</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7857,10 +7857,10 @@
         <v>2578.339317532384</v>
       </c>
       <c r="D421">
-        <v>1706.113834250452</v>
+        <v>1754.690399577438</v>
       </c>
       <c r="E421">
-        <v>3440.927229626017</v>
+        <v>3425.366753137194</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7874,10 +7874,10 @@
         <v>2598.492473290983</v>
       </c>
       <c r="D422">
-        <v>1778.11028502055</v>
+        <v>1692.568831287434</v>
       </c>
       <c r="E422">
-        <v>3485.37857020906</v>
+        <v>3435.742278078489</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7891,10 +7891,10 @@
         <v>2516.731454904884</v>
       </c>
       <c r="D423">
-        <v>1677.635527278649</v>
+        <v>1697.102297606712</v>
       </c>
       <c r="E423">
-        <v>3386.99182339443</v>
+        <v>3406.508385522251</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7908,10 +7908,10 @@
         <v>2724.9078442701</v>
       </c>
       <c r="D424">
-        <v>1879.885187670978</v>
+        <v>1881.49294977928</v>
       </c>
       <c r="E424">
-        <v>3527.89016296516</v>
+        <v>3586.379909282077</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7925,10 +7925,10 @@
         <v>2626.200331358057</v>
       </c>
       <c r="D425">
-        <v>1676.497072508721</v>
+        <v>1742.355593588274</v>
       </c>
       <c r="E425">
-        <v>3513.487178038266</v>
+        <v>3505.92331520087</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7942,10 +7942,10 @@
         <v>2930.606512861907</v>
       </c>
       <c r="D426">
-        <v>2070.468950138284</v>
+        <v>2058.883634162321</v>
       </c>
       <c r="E426">
-        <v>3798.152986534752</v>
+        <v>3856.365426733617</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7959,10 +7959,10 @@
         <v>2870.664341399954</v>
       </c>
       <c r="D427">
-        <v>1944.45909836474</v>
+        <v>2004.481518624325</v>
       </c>
       <c r="E427">
-        <v>3769.92901692634</v>
+        <v>3766.947580610976</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7976,10 +7976,10 @@
         <v>2575.312233409251</v>
       </c>
       <c r="D428">
-        <v>1651.362738035249</v>
+        <v>1709.609495343586</v>
       </c>
       <c r="E428">
-        <v>3447.783192600514</v>
+        <v>3447.254857829518</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7993,10 +7993,10 @@
         <v>2544.18924144711</v>
       </c>
       <c r="D429">
-        <v>1624.636374434989</v>
+        <v>1637.508219137992</v>
       </c>
       <c r="E429">
-        <v>3420.788036728883</v>
+        <v>3328.312697780645</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -8010,10 +8010,10 @@
         <v>2432.224192859864</v>
       </c>
       <c r="D430">
-        <v>1540.100681066259</v>
+        <v>1551.637737383355</v>
       </c>
       <c r="E430">
-        <v>3288.955716875985</v>
+        <v>3339.81902084733</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -8027,10 +8027,10 @@
         <v>2642.190134408244</v>
       </c>
       <c r="D431">
-        <v>1776.883631506622</v>
+        <v>1835.016313525148</v>
       </c>
       <c r="E431">
-        <v>3451.783926940219</v>
+        <v>3494.427757805459</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -8044,10 +8044,10 @@
         <v>2568.660602299092</v>
       </c>
       <c r="D432">
-        <v>1713.511371245551</v>
+        <v>1719.050622525696</v>
       </c>
       <c r="E432">
-        <v>3433.984004924034</v>
+        <v>3392.179929300164</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -8061,10 +8061,10 @@
         <v>2907.983223216532</v>
       </c>
       <c r="D433">
-        <v>2007.181688074804</v>
+        <v>2068.806229067411</v>
       </c>
       <c r="E433">
-        <v>3787.96127371887</v>
+        <v>3798.714806820692</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -8078,10 +8078,10 @@
         <v>2885.192115947498</v>
       </c>
       <c r="D434">
-        <v>2057.781441181715</v>
+        <v>2027.525857611177</v>
       </c>
       <c r="E434">
-        <v>3744.548912141459</v>
+        <v>3754.826596085821</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -8095,10 +8095,10 @@
         <v>2623.515625618763</v>
       </c>
       <c r="D435">
-        <v>1709.307563201839</v>
+        <v>1756.140914442062</v>
       </c>
       <c r="E435">
-        <v>3472.208586775098</v>
+        <v>3477.60639713725</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -8112,10 +8112,10 @@
         <v>2609.45554772162</v>
       </c>
       <c r="D436">
-        <v>1738.686935622803</v>
+        <v>1755.220290033898</v>
       </c>
       <c r="E436">
-        <v>3517.675319240047</v>
+        <v>3483.40676666804</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -8129,10 +8129,10 @@
         <v>2478.849642861285</v>
       </c>
       <c r="D437">
-        <v>1650.688090815507</v>
+        <v>1555.167890765116</v>
       </c>
       <c r="E437">
-        <v>3396.415459032295</v>
+        <v>3368.028150616065</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -8146,10 +8146,10 @@
         <v>2624.853311326682</v>
       </c>
       <c r="D438">
-        <v>1764.112807474135</v>
+        <v>1750.12276058739</v>
       </c>
       <c r="E438">
-        <v>3523.944639541616</v>
+        <v>3483.254443810288</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -8163,10 +8163,10 @@
         <v>2458.245342930465</v>
       </c>
       <c r="D439">
-        <v>1588.421810654318</v>
+        <v>1557.704090287192</v>
       </c>
       <c r="E439">
-        <v>3323.089166692256</v>
+        <v>3303.319793928376</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -8180,10 +8180,10 @@
         <v>2713.735805822446</v>
       </c>
       <c r="D440">
-        <v>1837.391726205791</v>
+        <v>1781.250533299841</v>
       </c>
       <c r="E440">
-        <v>3550.435183952844</v>
+        <v>3622.208775755899</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -8197,10 +8197,10 @@
         <v>2652.566905462816</v>
       </c>
       <c r="D441">
-        <v>1785.129936338614</v>
+        <v>1824.798810868918</v>
       </c>
       <c r="E441">
-        <v>3548.375795227489</v>
+        <v>3569.159248410215</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -8214,10 +8214,10 @@
         <v>2404.112257160305</v>
       </c>
       <c r="D442">
-        <v>1569.731479546785</v>
+        <v>1555.414918188638</v>
       </c>
       <c r="E442">
-        <v>3293.606053519958</v>
+        <v>3254.984867919541</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -8231,10 +8231,10 @@
         <v>2426.573866502401</v>
       </c>
       <c r="D443">
-        <v>1605.455512160835</v>
+        <v>1523.025366573177</v>
       </c>
       <c r="E443">
-        <v>3254.146686328744</v>
+        <v>3348.304466051188</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -8248,10 +8248,10 @@
         <v>2318.064598765412</v>
       </c>
       <c r="D444">
-        <v>1425.001333280186</v>
+        <v>1452.768841105934</v>
       </c>
       <c r="E444">
-        <v>3172.984206057324</v>
+        <v>3222.701817403641</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -8265,10 +8265,10 @@
         <v>2457.605579095085</v>
       </c>
       <c r="D445">
-        <v>1649.366639623885</v>
+        <v>1571.204962394151</v>
       </c>
       <c r="E445">
-        <v>3399.871043500907</v>
+        <v>3319.401599126955</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -8282,10 +8282,10 @@
         <v>2277.847327045339</v>
       </c>
       <c r="D446">
-        <v>1465.001708426626</v>
+        <v>1435.298070572729</v>
       </c>
       <c r="E446">
-        <v>3126.600087160269</v>
+        <v>3131.428994822247</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -8299,10 +8299,10 @@
         <v>2549.642730012506</v>
       </c>
       <c r="D447">
-        <v>1642.741455314842</v>
+        <v>1632.171132592319</v>
       </c>
       <c r="E447">
-        <v>3393.029807803243</v>
+        <v>3464.354417999194</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -8316,10 +8316,10 @@
         <v>2549.528751267353</v>
       </c>
       <c r="D448">
-        <v>1671.620582117423</v>
+        <v>1670.0340687799</v>
       </c>
       <c r="E448">
-        <v>3439.768228414475</v>
+        <v>3430.715315509312</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -8333,10 +8333,10 @@
         <v>2383.175993397896</v>
       </c>
       <c r="D449">
-        <v>1501.229408910116</v>
+        <v>1468.062389295578</v>
       </c>
       <c r="E449">
-        <v>3273.204271159931</v>
+        <v>3249.340606998763</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8350,10 +8350,10 @@
         <v>2463.917190443585</v>
       </c>
       <c r="D450">
-        <v>1631.2155298771</v>
+        <v>1637.67676304235</v>
       </c>
       <c r="E450">
-        <v>3290.781064428268</v>
+        <v>3363.612474239522</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8367,10 +8367,10 @@
         <v>2362.208862282596</v>
       </c>
       <c r="D451">
-        <v>1444.756299727585</v>
+        <v>1573.123289747402</v>
       </c>
       <c r="E451">
-        <v>3197.52999658569</v>
+        <v>3185.783521812716</v>
       </c>
     </row>
   </sheetData>
